--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="255">
   <si>
     <t>Date</t>
   </si>
@@ -1026,6 +1026,18 @@
   </si>
   <si>
     <t xml:space="preserve">Logistic regression model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">logistic model| how to check confusion matrix | 
+overfiting model &amp; underfiting model 
+preicics, recall, we build mode with scaling , without scaling, 
+what hapend when we change random state value = 0, 11, 21, 41, 51, 100 , result 0 
+we buidl ml model on historical data | model built 92.50% 
+share future data -- future data we need to pass to build in model and predict the future records for prediction 
+real time data vs prediction data ( ml testing -1 ) | 3 time for testing future records ( 85% ) pickle &amp; deployment </t>
+  </si>
+  <si>
+    <t>logistic &amp; knn</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2052,12 +2064,23 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" ht="162">
       <c r="A45" s="11">
         <v>46050</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>252</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="Project Tracking" sheetId="5" r:id="rId2"/>
-    <sheet name="sheet" sheetId="6" r:id="rId3"/>
+    <sheet name="EDA explanation" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'18th July - Agenda Sheet'!$A$1:$F$1</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="255">
   <si>
     <t>Date</t>
   </si>
@@ -747,38 +747,297 @@
     <t xml:space="preserve">eda practicle </t>
   </si>
   <si>
+    <t xml:space="preserve">OLAMA + STREAMLIT </t>
+  </si>
+  <si>
+    <t>EDA Practicle  &amp; Gradio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDA Practicle we apply all eda technique | Gradio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matplotlib workshop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seaborn workshop </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seaborn Bootcamp </t>
+  </si>
+  <si>
+    <t>Visualzation Using Matplotlib</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tTT7XJO30cM&amp;t=4358s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ChJEb5Usxug&amp;t=3958s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JhfTZ1QWN6A&amp;t=4561s</t>
+  </si>
+  <si>
+    <t>02-01-2026
+03-01-2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">raw data - clearn data ( remove reg ex)
-all eda technique apply clean data </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLAMA + STREAMLIT </t>
-  </si>
-  <si>
-    <t>EDA Practicle  &amp; Gradio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDA Practicle we apply all eda technique | Gradio </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matplotlib workshop </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seaborn workshop </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seaborn Bootcamp </t>
-  </si>
-  <si>
-    <t>Visualzation Using Matplotlib</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=tTT7XJO30cM&amp;t=4358s</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=ChJEb5Usxug&amp;t=3958s</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=JhfTZ1QWN6A&amp;t=4561s</t>
+all eda technique apply clean data 
+imputation, missing value treatment, graphs  
+Eda  we worked | we intrdouce to gradio </t>
+  </si>
+  <si>
+    <t>Eda Integration + LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eda  integration to llm </t>
+  </si>
+  <si>
+    <t>Eda integrattion + llm model 
+how llm model can integrate to dataset for pull the insgight
+chatpt -- any query -- respone genear from internet 
+prompt in python function ( prompt + llm model ) fetech the data from the dataset 
+we create gradio application you can upload any of the dataset it can pullout the data</t>
+  </si>
+  <si>
+    <t>Integration of llm model + dataset + ollama for automizaton the dataframe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">population &amp; sample 
+sampling technique -- from population to sampel | inference -- sample to population 
+descriptive stats -- central tendency ( mean, median, mode)
+skewness -- +Ve skew ( mean&gt; median &amp; Mode) data is at left outlier is at right
+-ve skew ( mode &gt; mean &amp; median) -- data is at right outlier is at left
+0 skew - mean = median = mode | normal distribute = gausian distribution = bell curve 
+variance -- spread of the data towards mean | standard deviation -- squrre root of variance 
+population mean - Mu, sample mean x- | population variance -- sigma 2 |sampel variance s2 
+population sd -- root of sigma 2 &amp; sample sd -- root of s2
++ve kurtois -- platykurtiv | -ve kur - lepto kurtic | 0 skew -- meso kurtic  </t>
+  </si>
+  <si>
+    <t>descriptive stats</t>
+  </si>
+  <si>
+    <t>Descriptive stats</t>
+  </si>
+  <si>
+    <t>Income expense descriptive stats analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complete .quntile() it will calculate the quartile | &lt;25% or &gt;75% what ever data points to outlier 
+inferential stat - probability &amp; disribution concept comes from probability 
+Roll 1 dice -- uniform distribution ( no meaning ) | Roll 2 dice -- normal distributeion 
+Normal distribution == Gausian distribuion == bell curve  
+confidence interval -- 2 interval point -- estimator &amp; average of 2 estimator is called estimates 
+95% &amp; 99% confidence  | if 95% confidence then error is called 5% 
+statsstic ml journey ( p-value == 0.05) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inferential stats -1 </t>
+  </si>
+  <si>
+    <t>Inferential stats -2</t>
+  </si>
+  <si>
+    <t>z score -- standarization conver mean 0 &amp; std - 1 
+z table , z-test ( data is population) 
+t test we will implement when the data is sample 
+p-value 0.05 cuz confidence is 95% \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adavance stats </t>
+  </si>
+  <si>
+    <t>Inferential stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales data anlaysis </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=baJi1276DcU&amp;t=10s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cofdenence interval -- 2 part 
+population -- z test | sample - t test 
+99% ml model while we build regression table we will get t-tst only not z-test 
+p-value =0.05 | y = mx + c | y^ = mx + c 
+y - actual point | y^ - predicted point | m- slope | x - iv, c -- intercept and constant 
+y = mx + C this equestion predict the future ?
+mae -- absoulte error ( actual - predicted ) | mse ( actual - predict) ** 2
+rmse -- root mean squre error np** sqrt (actual - predicte)**2  
+how to build inferential project &amp; also i shared some the link watch ( keep video)
+easy way to forget ( oops, stats )  -- reference 
+permormance measre of regression model -- r 2 &amp; adjusted r2 |  range 0-1 
+performance measure of classificaiton -- confusion matrix  
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANOVA, R2, ADJUSTED R2, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">anova -- analaysis of variance 
+Ssr == sum of squre regressor ( Predicted point - Avg point) 
+sse == sum of squre error ( Actual - Predicted) 
+sst = sse + ssr  ( actual - average)
+r2 &amp; adjusted r2 -- perfomance measure of regression model 
+range of r2 &amp; adjusted r2 0-1 | r2 &gt; adjusted r2
+regression table | we just menioned list of complete topics </t>
+  </si>
+  <si>
+    <t>Machine learning</t>
+  </si>
+  <si>
+    <t>ML -- DATA PREPROCESSING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">machine will learn the historical data 
+historical data -- 2 part ( training phase &amp; testing phase) 
+future data - validatiaon data 
+traditional learning vs machine learning 
+what is mean by model or logic 
+tradtional learning --- input right logic model generate output 
+machine learning -- train input data + output data -- logic has build ( model ) 
+introduce to spyder application  
+TRAIN TEST SPLIT RATIO -- 75-25 | 80-20 | 70-30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML introduction </t>
+  </si>
+  <si>
+    <t>Dataprocessing pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we buildild data preprocessing piple line 
+parameter tunning , hyperparameter tunning 
+sklearn framework | sklear.preprocessing |sklear.model_selection 
+labelencoder concept | train_test_split 
+what is the use to implement random_state = 0
+sklearn.imputer - which helps to fill missing value </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML developer code we built </t>
+  </si>
+  <si>
+    <t xml:space="preserve">simple linear regression model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we learned how to fit the simple liner reg algorithm 
+backend part , pickle the file frontend 
+once we build regressor model which hold simple linear regression algorithm 
+regressor.coef_ &amp; regressor.intercept) 
+cuz of 2 import concept anyone can predict the future datapoint
+how to compare actual data vs predicted data (y_test vs y_pred) 
+we train the historical data build model 
+pass validation data predict future prediction | future pred vs real time data </t>
+  </si>
+  <si>
+    <t xml:space="preserve">slr model performance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">slr model complete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">applie all stats concept to ml model 
+mae, mse, rmse , r2, sse, ssr, sst | corr
+knew that how to check best regression model 
+these concept only we discussed in stats concpet 
+yester backend part | bias -- training data &amp; variance - testign </t>
+  </si>
+  <si>
+    <t>SLR Backend code | deployment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">simple linear regression model we created frontend 
+backed &amp; fronted . Pickle file can save the as wb file 
+frontend used those load the pickle create a project 
+multiple linear regression algoriytm 
+ml devloper need to sugest fridnds organizatino which produc need to inverst more profit
+build ml mlr alog with rfe concept , anova table </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLR model </t>
+  </si>
+  <si>
+    <t>https://www.statsmodels.org/stable/api.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mlr </t>
+  </si>
+  <si>
+    <t>multiple linear regression model</t>
+  </si>
+  <si>
+    <t>slr model &amp; mlr model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">House price prediction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regualariztion technique </t>
+  </si>
+  <si>
+    <t>we buitl multiple lienar lregression model 
+how to add constat to the dataset using np.append
+we build regrssion table | p-value | based on highest we elimate the attribute
+we find out the attribute  | overfitting -- train the model with more data 
+underfitting - train the data with less data | technique to reduce underfit -- add more relavant attribute  
+Technique to reduce overfit -- pca, regularization, cross validation, ensamble learnin, dropout the neurons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">polynomial model </t>
+  </si>
+  <si>
+    <t>Regualarize the coefficient of independent values | 3 types of regularization -- l1, l2, elasticnet 
+L1 - lasso -- regularized the coeff to 0 | we call this concept as feature elimination technique 
+L2 - Ridge -- regularize the high coef - low coef but not 0 
+elasticnet -- l1 + l2 (combination of lasso &amp; ridge) | feature scaling technique - standarization, normalization ( we can apply both but bydefault parameter -- standasclaer ( normal distribution)
+FEATURE SELECTION ( business , l1, rfe using p-value) vs FEATURE SCALING vs FEATURE ENGINEERING ( eda tech)</t>
+  </si>
+  <si>
+    <t>Regularization project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cars mpg analysis using l1, l2, simple linear model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">non linear model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">polynomial model with hyperparameter tunning -- 174.8 -- 6.5 level  
+svr model -- 164 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">polynomial -- Increse the degree of independent variable 
+we build the code yesterday without train &amp; test split we built
+svr model | using hyperparameter tunning accuracy increse
+parameter tunning if accuracy will increase  </t>
+  </si>
+  <si>
+    <t>knn, dt, rf  | intro classfiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knn model | svr model | DT R model | Rf reGRESSION MODEL 
+one dataset we will several model -- best accuracy model pickle it deploy to the frontend
+confusion matrix -- TP , TN , FP, FN 
+accuracy -- tp+tn/total, error rate -- fp+fn/total , precion - tp /predicted yes , recall - tp / actual yes 
+fp - type 1 error &amp; fn -- type 2 error 
+why logistic regression called as classification , what could be the reason we intoduce probability function
+to handle outlier in the data intoduce sigmoid function | range of S curve - 0-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logistic regression model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">logistic model| how to check confusion matrix | 
+overfiting model &amp; underfiting model 
+preicics, recall, we build mode with scaling , without scaling, 
+what hapend when we change random state value = 0, 11, 21, 41, 51, 100 , result 0 
+we buidl ml model on historical data | model built 92.50% 
+share future data -- future data we need to pass to build in model and predict the future records for prediction 
+real time data vs prediction data ( ml testing -1 ) | 3 time for testing future records ( 85% ) pickle &amp; deployment </t>
+  </si>
+  <si>
+    <t>logistic &amp; knn</t>
   </si>
 </sst>
 </file>
@@ -1306,12 +1565,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="107.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="116.109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="53.44140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="34.77734375" style="3" customWidth="1"/>
     <col min="6" max="6" width="49.88671875" style="3" customWidth="1"/>
@@ -1475,7 +1734,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="90">
+    <row r="15" spans="1:6" ht="72">
       <c r="A15" s="11">
         <v>46003</v>
       </c>
@@ -1629,15 +1888,199 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="36">
-      <c r="A29" s="11">
-        <v>46024</v>
+    <row r="29" spans="1:3" ht="90.6" customHeight="1">
+      <c r="A29" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>190</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="90">
+      <c r="A30" s="11">
+        <v>46027</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="180">
+      <c r="A31" s="11">
+        <v>46028</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="126">
+      <c r="A32" s="11">
+        <v>46029</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="72">
+      <c r="A33" s="11">
+        <v>46030</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="216.6" customHeight="1">
+      <c r="A34" s="11">
+        <v>46031</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="126">
+      <c r="A35" s="11">
+        <v>46032</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="168" customHeight="1">
+      <c r="A36" s="11">
+        <v>46034</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="108">
+      <c r="A37" s="11">
+        <v>46041</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="144">
+      <c r="A38" s="11">
+        <v>46042</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="90">
+      <c r="A39" s="11">
+        <v>46043</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="108">
+      <c r="A40" s="11">
+        <v>46044</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="108">
+      <c r="A41" s="11">
+        <v>46045</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="126">
+      <c r="A42" s="11">
+        <v>46046</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="72">
+      <c r="A43" s="11">
+        <v>46048</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="126">
+      <c r="A44" s="11">
+        <v>46049</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="162">
+      <c r="A45" s="11">
+        <v>46050</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="11">
+        <v>46051</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -1654,7 +2097,7 @@
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="79.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="71.77734375" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -1720,7 +2163,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="62.4">
+    <row r="3" spans="1:11" ht="93.6">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -1900,7 +2343,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="31.2">
+    <row r="12" spans="1:11" ht="46.8">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2040,7 +2483,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" ht="31.2">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -2080,7 +2523,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" ht="31.2">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -2173,7 +2616,7 @@
         <v>124</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -2190,13 +2633,13 @@
         <v>46025</v>
       </c>
       <c r="C26" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>193</v>
-      </c>
       <c r="E26" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
@@ -2212,13 +2655,13 @@
         <v>46025</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
@@ -2234,13 +2677,13 @@
         <v>46025</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>196</v>
-      </c>
       <c r="E28" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
@@ -2248,8 +2691,19 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10">
-      <c r="D29" s="6"/>
+    <row r="29" spans="1:10" ht="31.2">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>205</v>
+      </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
@@ -2258,7 +2712,18 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="D30" s="6"/>
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
@@ -2267,8 +2732,21 @@
       <c r="J30" s="6"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -2276,7 +2754,18 @@
       <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="D32" s="6"/>
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>224</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
@@ -2284,8 +2773,19 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="4:10">
-      <c r="D33" s="6"/>
+    <row r="33" spans="1:10">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>227</v>
+      </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
@@ -2293,17 +2793,41 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="4:10">
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+    <row r="34" spans="1:10">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>236</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="4:10">
-      <c r="D35" s="6"/>
+    <row r="35" spans="1:10">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>239</v>
+      </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
@@ -2311,8 +2835,19 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="4:10">
-      <c r="D36" s="6"/>
+    <row r="36" spans="1:10">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>246</v>
+      </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
@@ -2320,8 +2855,19 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="4:10">
-      <c r="D37" s="6"/>
+    <row r="37" spans="1:10" ht="31.2">
+      <c r="A37" s="9">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>248</v>
+      </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
@@ -2329,7 +2875,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="4:10">
+    <row r="38" spans="1:10">
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -2338,7 +2884,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="4:10">
+    <row r="39" spans="1:10">
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2347,7 +2893,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="4:10">
+    <row r="40" spans="1:10">
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -2356,7 +2902,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="4:10">
+    <row r="41" spans="1:10">
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -2365,7 +2911,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="4:10">
+    <row r="42" spans="1:10">
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -2374,7 +2920,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="4:10">
+    <row r="43" spans="1:10">
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -2383,7 +2929,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="4:10">
+    <row r="44" spans="1:10">
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -2392,7 +2938,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="4:10">
+    <row r="45" spans="1:10">
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -2401,7 +2947,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="4:10">
+    <row r="46" spans="1:10">
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -2410,7 +2956,7 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
     </row>
-    <row r="47" spans="4:10">
+    <row r="47" spans="1:10">
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
@@ -2419,7 +2965,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="4:10">
+    <row r="48" spans="1:10">
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="261">
   <si>
     <t>Date</t>
   </si>
@@ -1038,6 +1038,32 @@
   </si>
   <si>
     <t>logistic &amp; knn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logistic regression </t>
+  </si>
+  <si>
+    <t>logitis regression model with hyperapareamter,apply validation data</t>
+  </si>
+  <si>
+    <t>KNN classifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vechicl purchase dataset knn classiifcaiton model compare with logistic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">how to pass validation data or future data to the build in models 
+model predicts the future records | compare with future pred vs live data 
+3phase sof model testing will be going on. We take average of 3 phases then deployment 
+knn -- k nearest neighbour | decission will be take based the neighbour 
+knn distance matrix | EU - euclidian distance matrix | MD - manhatten distance matrix 
+ED - shortest distance | MD - Farthest distance 
+when we built knn model we discuss about all the model 
+ML MODEL PARAMETER vs LLM MODEL PARAMETER 
+how knn model impacted by outerlier and logistic model doesnot impacted by outlier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">knn &amp; svm </t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2075,12 +2101,23 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" ht="162">
       <c r="A46" s="11">
         <v>46051</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>254</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="11">
+        <v>46052</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -2876,7 +2913,18 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="D38" s="6"/>
+      <c r="A38" s="9">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
@@ -2885,7 +2933,18 @@
       <c r="J38" s="6"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="D39" s="6"/>
+      <c r="A39" s="9">
+        <v>38</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="267">
   <si>
     <t>Date</t>
   </si>
@@ -1046,9 +1046,6 @@
     <t>logitis regression model with hyperapareamter,apply validation data</t>
   </si>
   <si>
-    <t>KNN classifier</t>
-  </si>
-  <si>
     <t xml:space="preserve">vechicl purchase dataset knn classiifcaiton model compare with logistic </t>
   </si>
   <si>
@@ -1064,6 +1061,33 @@
   </si>
   <si>
     <t xml:space="preserve">knn &amp; svm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">imbalance data -- smote technique ( synthetic minority oversampling technique) 
+majority class vs minority class | downsample majority class &amp; overfsampel minority classes 
+slr vs svr -- best fit line vs hyperplane | data point which close to the hyperplacen we plot the parael line 
+decission boudry or suport vector line | distance between 2 svr line is called maximu marginal distance 
+why we need to check max marginal distance cuz to adjust the more error  |
+svm code -- ac -- 95 | non liear to linear function -- kernal function -- poly, sigmoid, rbf, linera, liblinear, sag, saga | kernel function -- dimension increase | dimension reduction -- pca  
+naive bayes -- conditional prob, bayes theorem </t>
+  </si>
+  <si>
+    <t>Naïve Bayes</t>
+  </si>
+  <si>
+    <t>SVM Classifier</t>
+  </si>
+  <si>
+    <t>KNN Classifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vechicl purchase dataset knn classiifcaiton model compare with logit, svm  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naïve Bayes </t>
+  </si>
+  <si>
+    <t>vechicl purchase dataset knn classiifcaiton model compare with logit, svm , knn</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2109,15 +2133,26 @@
         <v>254</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="144">
       <c r="A47" s="11">
         <v>46052</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="11">
+        <v>46055</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2169,7 @@
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.77734375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="74.44140625" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -2940,10 +2975,10 @@
         <v>46051</v>
       </c>
       <c r="C39" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>257</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>258</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2953,7 +2988,18 @@
       <c r="J39" s="6"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="D40" s="6"/>
+      <c r="A40" s="9">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
@@ -2961,8 +3007,19 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10">
-      <c r="D41" s="6"/>
+    <row r="41" spans="1:10" ht="31.2">
+      <c r="A41" s="9">
+        <v>40</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46055</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>266</v>
+      </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="271">
   <si>
     <t>Date</t>
   </si>
@@ -1081,13 +1081,28 @@
     <t>KNN Classifier</t>
   </si>
   <si>
-    <t xml:space="preserve">vechicl purchase dataset knn classiifcaiton model compare with logit, svm  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Naïve Bayes </t>
   </si>
   <si>
-    <t>vechicl purchase dataset knn classiifcaiton model compare with logit, svm , knn</t>
+    <t xml:space="preserve">what is naïve in naïve bayes | conditional probability 
+bays theorem | bayesian theorem | prior prob, posterior, marginal, liklihood
+bernoulli, multinomial , gausian naïve bayes | gausina naïve bayes does not required feature scaling 
+how this algoriyt play very import role on booking  this is one of the prob algorithm in machine learning </t>
+  </si>
+  <si>
+    <t>Tree Algorithm</t>
+  </si>
+  <si>
+    <t>Decission tree model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vechicl purchase dataset  classiifcaiton model compare with logit, svm  </t>
+  </si>
+  <si>
+    <t>vechicl purchase dataset classiifcaiton model compare with logit, svm , knn</t>
+  </si>
+  <si>
+    <t>vechicl purchase dataset classiifcaiton model compare with logit, svm , knn, NB</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2147,12 +2162,23 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" ht="72">
       <c r="A48" s="11">
         <v>46055</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>261</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="11">
+        <v>46056</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2169,7 +2195,7 @@
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.44140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="80.33203125" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -2595,7 +2621,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="31.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -2763,7 +2789,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" ht="31.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -2998,7 +3024,7 @@
         <v>263</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -3007,7 +3033,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" ht="31.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -3015,10 +3041,10 @@
         <v>46055</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -3028,7 +3054,18 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="D42" s="6"/>
+      <c r="A42" s="9">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="273">
   <si>
     <t>Date</t>
   </si>
@@ -1103,6 +1103,19 @@
   </si>
   <si>
     <t>vechicl purchase dataset classiifcaiton model compare with logit, svm , knn, NB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensamble learning </t>
+  </si>
+  <si>
+    <t>How to build decission tree from the dataset 
+how to declare root node | sub root node  | gini , entropy, information gain calculation 
+when we build the tree indepth overfitting problems will happen 
+remove the irrelavant atribute | ml parameters | when to best split and random split 
+random split -- every run accuracy are varies | best split 
+decission tree doesnot required feature scaling | dt model 
+dataset -- db or client -- datware house -- dv -- regress mode, classifiction 
+clusterin no dv | auc &amp; roc curve is graph of confusion matrix | x axis -- FPR (sensitivity) vs 1-specificity ( TPR)</t>
   </si>
 </sst>
 </file>
@@ -1630,12 +1643,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="38.44140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="116.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="121.21875" style="3" customWidth="1"/>
     <col min="4" max="4" width="53.44140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="34.77734375" style="3" customWidth="1"/>
     <col min="6" max="6" width="49.88671875" style="3" customWidth="1"/>
@@ -2173,12 +2186,23 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:3" ht="162">
       <c r="A49" s="11">
         <v>46056</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>266</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="11">
+        <v>46057</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2285,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="93.6">
+    <row r="3" spans="1:11" ht="62.4">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2441,7 +2465,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="46.8">
+    <row r="12" spans="1:11" ht="31.2">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2581,7 +2605,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="31.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="9">
         <v>18</v>
       </c>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="283">
   <si>
     <t>Date</t>
   </si>
@@ -1116,6 +1116,48 @@
 decission tree doesnot required feature scaling | dt model 
 dataset -- db or client -- datware house -- dv -- regress mode, classifiction 
 clusterin no dv | auc &amp; roc curve is graph of confusion matrix | x axis -- FPR (sensitivity) vs 1-specificity ( TPR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensamble learning -- Bagging, boosting 
+random forest -- bagging concept | how ensamble learning reduce overfitting 
+boosting is sequential cuz every time we built the tree with error 
+boosting -- xgboost &amp; lgbm | dataset -- dv -- regression, classificaiton model 
+make sure one dataset you need to build all the models 
+random forest random state parameter must need to define random forest we are completed </t>
+  </si>
+  <si>
+    <t>Boosting framwork, Cross validation</t>
+  </si>
+  <si>
+    <t>https://www.kaggle.com/code/prashant111/knn-classifier-tutorial
+https://www.kaggle.com/code/prashant111/naive-bayes-classifier-in-python
+https://www.kaggle.com/code/prashant111/xgboost-k-fold-cv-feature-importance 
+https://www.kaggle.com/code/prashant111/lightgbm-classifier-in-python
+https://www.kaggle.com/code/prashant111/decision-tree-classifier-tutorial
+https://www.kaggle.com/code/prashant111/a-guide-on-xgboost-hyperparameters-tuning
+https://www.kaggle.com/code/prashant111/bagging-vs-boosting
+https://www.kaggle.com/code/prashant111/adaboost-classifier-tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer churn prediction </t>
+  </si>
+  <si>
+    <t>using xgboost model we build the customer churn</t>
+  </si>
+  <si>
+    <t>bagging, boosting, adaboot, decission tree, lightgbm , kfold</t>
+  </si>
+  <si>
+    <t>43-50</t>
+  </si>
+  <si>
+    <t>Ml capstone project  ( Regression &amp; Classification)</t>
+  </si>
+  <si>
+    <t>churn modeling || customer churn || crypot analysis || customer churn telecome domain || diabetic prediction || heart disease || height &amp; weight prediction || housing regressor || iris using flask || loan approval prediction || movie genere || movie review analysis</t>
+  </si>
+  <si>
+    <t>51-60</t>
   </si>
 </sst>
 </file>
@@ -1643,11 +1685,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="41" style="3" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" customWidth="1"/>
     <col min="4" max="4" width="53.44140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="34.77734375" style="3" customWidth="1"/>
@@ -1889,7 +1931,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="162">
+    <row r="22" spans="1:3" ht="144">
       <c r="A22" s="11">
         <v>46013</v>
       </c>
@@ -2142,7 +2184,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="162">
+    <row r="45" spans="1:3" ht="144">
       <c r="A45" s="11">
         <v>46050</v>
       </c>
@@ -2186,7 +2228,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="162">
+    <row r="49" spans="1:3" ht="144">
       <c r="A49" s="11">
         <v>46056</v>
       </c>
@@ -2197,12 +2239,23 @@
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" ht="108">
       <c r="A50" s="11">
         <v>46057</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>271</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="11">
+        <v>46058</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -2213,13 +2266,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K278"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.33203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="84.109375" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -3098,7 +3151,18 @@
       <c r="J42" s="6"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="D43" s="6"/>
+      <c r="A43" s="9">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46057</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>277</v>
+      </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
@@ -3106,8 +3170,19 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10">
-      <c r="D44" s="6"/>
+    <row r="44" spans="1:10" ht="62.4">
+      <c r="A44" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46057</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>281</v>
+      </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
@@ -3115,23 +3190,25 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10">
-      <c r="D45" s="6"/>
+    <row r="45" spans="1:10" ht="140.4">
+      <c r="A45" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46058</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>275</v>
+      </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
     </row>
     <row r="47" spans="1:10">
       <c r="D47" s="6"/>
@@ -5220,6 +5297,24 @@
       <c r="H278" s="6"/>
       <c r="I278" s="6"/>
       <c r="J278" s="6"/>
+    </row>
+    <row r="279" spans="4:10">
+      <c r="D279" s="6"/>
+      <c r="E279" s="6"/>
+      <c r="F279" s="6"/>
+      <c r="G279" s="6"/>
+      <c r="H279" s="6"/>
+      <c r="I279" s="6"/>
+      <c r="J279" s="6"/>
+    </row>
+    <row r="280" spans="4:10">
+      <c r="D280" s="6"/>
+      <c r="E280" s="6"/>
+      <c r="F280" s="6"/>
+      <c r="G280" s="6"/>
+      <c r="H280" s="6"/>
+      <c r="I280" s="6"/>
+      <c r="J280" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="300">
   <si>
     <t>Date</t>
   </si>
@@ -1126,9 +1126,6 @@
 random forest random state parameter must need to define random forest we are completed </t>
   </si>
   <si>
-    <t>Boosting framwork, Cross validation</t>
-  </si>
-  <si>
     <t>https://www.kaggle.com/code/prashant111/knn-classifier-tutorial
 https://www.kaggle.com/code/prashant111/naive-bayes-classifier-in-python
 https://www.kaggle.com/code/prashant111/xgboost-k-fold-cv-feature-importance 
@@ -1158,6 +1155,74 @@
   </si>
   <si>
     <t>51-60</t>
+  </si>
+  <si>
+    <t>Boosting framwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cross validation  &amp; clustering </t>
+  </si>
+  <si>
+    <t>xgboost is another framework act like sklearn 
+ml model frameworks | lgbm -- light gradeint boosting machine which is 6time faster then xgb 
+we worked yesterday project | customer churn prediction 
+yesterday I shared some project link please work on them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k-means &amp; hierarchical clustering &amp; dbscan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">k-fold cv -- when the models are overfiting there we implement k fold cv 
+dataset we divide into 1000 records divided into 5 fold . Each folds contain 200 recording build model 5 times 
+average of all the 5 models then we calculate ( reduce high var - low var ) reduce overfitting technique 
+model tunning -- gridsearch cv &amp; random search cv 
+we pass each and every model parameters ( manually assigne all the parameter in one go) grid search cv will finetune optimized parameter  | discussed math for k-meas
+clustering -- grouping | no dependent variable | data is discreate we are using 
+customer segmentation, rating the food, grading score student  | elbow method -- will decide how to make cluster from the dataset | xaxias - number of cluster &amp; y axis - wcss (within cluster sum of squard) </t>
+  </si>
+  <si>
+    <t>cross validation</t>
+  </si>
+  <si>
+    <t>K-fold cross validation | grid search cv | random search cv</t>
+  </si>
+  <si>
+    <t>k means clustering</t>
+  </si>
+  <si>
+    <t>customer segmentation project</t>
+  </si>
+  <si>
+    <t>Hierarchicla clustering</t>
+  </si>
+  <si>
+    <t>kmeans preacticel we worked, hierachical cluster -- 2 part 
+agglomerative clustering -- using dendogram we build the cluster from bottom to top approach
+divisive clusterin -- divide the cluster from bottom to top approach 
+both we practicle we worked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pca , dbscan, intro nlp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pca ( principal componenet anlaysis) -- reduce the high dimension to low dimension ( dimension reduction technique) | kernal function -- increase (low dimension to high dimension)
+dbscan -- clustering algo which require min 3 point to have core point &amp; boundry point 
+noise point which is outlier | nlp we install framework -- nltk | nlp -- nlu &amp; nlg | day by day text are increasing | comments, chats | nlu tokeization -- tokens words | word_tokenzie, sent_tokenize | blankline_tokenzie | whitespace_tokenize ( text cleanin) | </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pca cluster image file I shared </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP Intro </t>
+  </si>
+  <si>
+    <t>NLU &amp; NLG</t>
+  </si>
+  <si>
+    <t>NLP Algorithm</t>
   </si>
 </sst>
 </file>
@@ -1685,7 +1750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2250,12 +2315,48 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" ht="72">
       <c r="A51" s="11">
         <v>46058</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>274</v>
+        <v>282</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="162">
+      <c r="A52" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="72">
+      <c r="A53" s="11">
+        <v>46060</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="108">
+      <c r="A54" s="11">
+        <v>46062</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -3158,10 +3259,10 @@
         <v>46057</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -3172,16 +3273,16 @@
     </row>
     <row r="44" spans="1:10" ht="62.4">
       <c r="A44" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B44" s="10">
         <v>46057</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -3192,16 +3293,16 @@
     </row>
     <row r="45" spans="1:10" ht="140.4">
       <c r="A45" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B45" s="10">
         <v>46058</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -3210,8 +3311,33 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="9">
+        <v>61</v>
+      </c>
+      <c r="B46" s="10">
+        <v>46059</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>288</v>
+      </c>
+    </row>
     <row r="47" spans="1:10">
-      <c r="D47" s="6"/>
+      <c r="A47" s="9">
+        <v>62</v>
+      </c>
+      <c r="B47" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>290</v>
+      </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
@@ -3220,7 +3346,18 @@
       <c r="J47" s="6"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="D48" s="6"/>
+      <c r="A48" s="9">
+        <v>63</v>
+      </c>
+      <c r="B48" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>290</v>
+      </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
@@ -3228,8 +3365,19 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="4:10">
-      <c r="D49" s="6"/>
+    <row r="49" spans="1:10">
+      <c r="A49" s="9">
+        <v>64</v>
+      </c>
+      <c r="B49" s="10">
+        <v>46062</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>296</v>
+      </c>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
@@ -3237,8 +3385,19 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="4:10">
-      <c r="D50" s="6"/>
+    <row r="50" spans="1:10">
+      <c r="A50" s="9">
+        <v>65</v>
+      </c>
+      <c r="B50" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>298</v>
+      </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
@@ -3246,7 +3405,16 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="4:10">
+    <row r="51" spans="1:10">
+      <c r="A51" s="9">
+        <v>66</v>
+      </c>
+      <c r="B51" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>299</v>
+      </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
@@ -3255,7 +3423,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="4:10">
+    <row r="52" spans="1:10">
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
@@ -3264,7 +3432,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="4:10">
+    <row r="53" spans="1:10">
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
@@ -3273,7 +3441,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="4:10">
+    <row r="54" spans="1:10">
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
@@ -3282,7 +3450,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="4:10">
+    <row r="55" spans="1:10">
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
@@ -3291,7 +3459,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="4:10">
+    <row r="56" spans="1:10">
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
@@ -3300,7 +3468,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="4:10">
+    <row r="57" spans="1:10">
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
@@ -3309,7 +3477,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="4:10">
+    <row r="58" spans="1:10">
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
@@ -3318,7 +3486,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="4:10">
+    <row r="59" spans="1:10">
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -3327,7 +3495,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="4:10">
+    <row r="60" spans="1:10">
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -3336,7 +3504,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="4:10">
+    <row r="61" spans="1:10">
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -3345,7 +3513,7 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="4:10">
+    <row r="62" spans="1:10">
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -3354,7 +3522,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="4:10">
+    <row r="63" spans="1:10">
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -3363,7 +3531,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="4:10">
+    <row r="64" spans="1:10">
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="306">
   <si>
     <t>Date</t>
   </si>
@@ -1219,10 +1219,30 @@
     <t xml:space="preserve">NLP Intro </t>
   </si>
   <si>
-    <t>NLU &amp; NLG</t>
-  </si>
-  <si>
     <t>NLP Algorithm</t>
+  </si>
+  <si>
+    <t>Natural Language Understanding  &amp; Natural Language Generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP Introduction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP Algorithm | Word embedding </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLU - tokenization, stemming, lematization, stopwords, NER, POS 
+NLG - wordcloud ( text visualization) | practicles we worked 
+ne_chunk is one functionalitry from NER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOW &amp; TFIDF </t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Customer review anlaysis | sentiment anlaysis for customer feedback</t>
   </si>
 </sst>
 </file>
@@ -1750,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2357,6 +2377,25 @@
       </c>
       <c r="C54" s="2" t="s">
         <v>294</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="54">
+      <c r="A55" s="11">
+        <v>46063</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="11">
+        <v>46064</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3396,7 +3435,7 @@
         <v>297</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -3410,12 +3449,14 @@
         <v>66</v>
       </c>
       <c r="B51" s="10">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="D51" s="6"/>
+        <v>298</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>303</v>
+      </c>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
@@ -3424,7 +3465,18 @@
       <c r="J51" s="6"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="D52" s="6"/>
+      <c r="A52" s="9">
+        <v>67</v>
+      </c>
+      <c r="B52" s="10">
+        <v>46064</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>305</v>
+      </c>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="329">
   <si>
     <t>Date</t>
   </si>
@@ -1243,6 +1243,81 @@
   </si>
   <si>
     <t>Customer review anlaysis | sentiment anlaysis for customer feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bow -- bag of words -- convert text to number ( words repet 2 times -- 2) 
+tfidf -- tf * Idf ( words are calcuated to log caluculation -- decimal value) 
+nlp -- text -- text clean -- as per the requirement -- text will convert number 0 &amp; 1 then we imple all ml models
+nlp -- text -- word extraction -- ml clustering as well | nltk library we understand </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spacy </t>
+  </si>
+  <si>
+    <t>Spacy introduction | Text summarization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLP </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the simple rule based chatbot </t>
+  </si>
+  <si>
+    <t>spacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spacy is more advanced then nltk | one line code we complete all nlu technique 
+load en_core_web_sm | 326 stopwords spacy | text summariozation | token scoring | sentence scoring 
+heapq -- largest , nsmallest, built the chatbot </t>
+  </si>
+  <si>
+    <t>NLP PROJECT</t>
+  </si>
+  <si>
+    <t>multilanguage bot we built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">language translator with wordcloud, voice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">poc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">text to sppech for mail voice &amp; female voice </t>
+  </si>
+  <si>
+    <t xml:space="preserve">xml scrappint &amp; webscrippin </t>
+  </si>
+  <si>
+    <t>few kaggle links  &amp; xml scrappin</t>
+  </si>
+  <si>
+    <t>NLP Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multilanguage translation </t>
+  </si>
+  <si>
+    <t>spacy introductin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text summarization usins spacy | how to install spacy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text cleaning </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text cleaning xml scrapping | end to end nlp we discused </t>
+  </si>
+  <si>
+    <t xml:space="preserve">spacy introduce , text summarization, multilat translation
+text -- how to implement ml model we learned.. Regression, classification, cluster </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEEP LEARNING </t>
+  </si>
+  <si>
+    <t>NLP</t>
   </si>
 </sst>
 </file>
@@ -1770,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2390,12 +2465,45 @@
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" ht="72">
       <c r="A56" s="11">
         <v>46064</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>301</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="54">
+      <c r="A57" s="11">
+        <v>46065</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="36">
+      <c r="A58" s="11">
+        <v>46066</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="11">
+        <v>46069</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -3484,8 +3592,19 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10">
-      <c r="D53" s="6"/>
+    <row r="53" spans="1:10" ht="18">
+      <c r="A53" s="9">
+        <v>68</v>
+      </c>
+      <c r="B53" s="10">
+        <v>46065</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
@@ -3494,7 +3613,18 @@
       <c r="J53" s="6"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="D54" s="6"/>
+      <c r="A54" s="9">
+        <v>69</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46065</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>310</v>
+      </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
@@ -3503,7 +3633,18 @@
       <c r="J54" s="6"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="D55" s="6"/>
+      <c r="A55" s="9">
+        <v>70</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>314</v>
+      </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
@@ -3512,7 +3653,18 @@
       <c r="J55" s="6"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="D56" s="6"/>
+      <c r="A56" s="9">
+        <v>71</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>315</v>
+      </c>
       <c r="E56" s="6"/>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
@@ -3521,7 +3673,18 @@
       <c r="J56" s="6"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="D57" s="6"/>
+      <c r="A57" s="9">
+        <v>72</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>317</v>
+      </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
@@ -3530,7 +3693,18 @@
       <c r="J57" s="6"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="D58" s="6"/>
+      <c r="A58" s="9">
+        <v>73</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>319</v>
+      </c>
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
@@ -3539,7 +3713,18 @@
       <c r="J58" s="6"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="D59" s="6"/>
+      <c r="A59" s="9">
+        <v>74</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>321</v>
+      </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
@@ -3548,7 +3733,18 @@
       <c r="J59" s="6"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="D60" s="6"/>
+      <c r="A60" s="9">
+        <v>75</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>323</v>
+      </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
@@ -3557,7 +3753,18 @@
       <c r="J60" s="6"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="D61" s="6"/>
+      <c r="A61" s="9">
+        <v>76</v>
+      </c>
+      <c r="B61" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>325</v>
+      </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="330">
   <si>
     <t>Date</t>
   </si>
@@ -1314,10 +1314,22 @@
 text -- how to implement ml model we learned.. Regression, classification, cluster </t>
   </si>
   <si>
-    <t xml:space="preserve">DEEP LEARNING </t>
-  </si>
-  <si>
     <t>NLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEEP LEARNING -- ANN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human neural network vs Artificial Neural network 
+neurons, signal , nerural network, weight assignment, weight adjusted, input, hidden , outpuer
+singly layer nn vs multi layer nn | forward prop weighs are assgined | back proper weight adjusted 
+new weight = old weigh - learnin * der loss/ der of old | input layer activation function not reuqie 
+hidden layer and output layer actiation function rquierd 
+sigmoid activation funciton -- output layer, range -- 0 1 | tanh apply output layer -- -1 to 1 
+relu activation we implement in hidden layer | leeky relu we implement in -- hidden layer 
+softmax activation function we implement in output layer range 0-1 | prob function 
+optimizer -- adam, adadelta, adagrade, adamax, rmsprop 
+loss - mae, mse, log loss, | classification -- binary cross entropy, category cross entropy, sparse category cross entropy | install of tf, keras, torch, ultrayltics, medipipe, opencv langchain, langgraph &amp; how to create env variable for your projects  | EPOC | NEURAL NETWORK ARCHITECTURE </t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2492,18 +2504,26 @@
         <v>46066</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" ht="216">
       <c r="A59" s="11">
         <v>46069</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="11">
+        <v>46070</v>
       </c>
     </row>
   </sheetData>
@@ -3592,17 +3612,17 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10" ht="18">
+    <row r="53" spans="1:10">
       <c r="A53" s="9">
         <v>68</v>
       </c>
       <c r="B53" s="10">
         <v>46065</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="8" t="s">
         <v>308</v>
       </c>
       <c r="E53" s="6"/>
@@ -3773,6 +3793,9 @@
       <c r="J61" s="6"/>
     </row>
     <row r="62" spans="1:10">
+      <c r="A62" s="9">
+        <v>77</v>
+      </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B7F7E-E73B-4B81-9ED9-6F8DBA0FE303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23172" windowHeight="9624" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -15,22 +21,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'18th July - Agenda Sheet'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="342">
   <si>
     <t>Date</t>
   </si>
@@ -1331,12 +1326,64 @@
 optimizer -- adam, adadelta, adagrade, adamax, rmsprop 
 loss - mae, mse, log loss, | classification -- binary cross entropy, category cross entropy, sparse category cross entropy | install of tf, keras, torch, ultrayltics, medipipe, opencv langchain, langgraph &amp; how to create env variable for your projects  | EPOC | NEURAL NETWORK ARCHITECTURE </t>
   </si>
+  <si>
+    <t>Deep Learning - ANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we built ANN model with single layer and 2 layer architecutre 
+tf.keras.sequentiatl - establish the layer | ann.add( neuron &amp; densely connect, activate relu)
+ann.add ( hidden layer) -- ann.add( sigmoid) as we worked on  binary class classification 
+optimizer -- adam, loss -- binary cross entropy, epoch , batchsize = 32 
+build ann model </t>
+  </si>
+  <si>
+    <t>CNN - 1</t>
+  </si>
+  <si>
+    <t>CNN - 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human vision vs computer vision 
+human - see any image -- brain ever cerbral layer wise 
+computer vision -- convoluion layer , max pool, flatten &amp; fully connected layer
+image -- matrix ( size will be more when image has more clarity matrix will define |pixel size 0-255
+cnn -- input matrix * filter = output matrix | filter - feature detector | output -- feature map 
+convolution layer is math calculat filter will apply on input matrix to calculate otuput matrix | bydefault strding  is 1 | s = 1 | input matrix ! = output matrix | padding concept -- p=1 ( it iwll all 4 part to pad repalce with 0) 
+</t>
+  </si>
+  <si>
+    <t>Image classification</t>
+  </si>
+  <si>
+    <t>happy or sad classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we have few images | train test validation 
+train &amp; validation -- we create 2 folder happy face &amp; sad faces 
+testing -- pass few random images in both folder 
+image shpas are happening how image are convered to array
+.flow_from_directory (train &amp; test) rms prop optimizer loss function -- binarycross entropy activation relu,
+ conv2d, maxpool2d, flatten &amp; integrated to gradio application to detec
+</t>
+  </si>
+  <si>
+    <t>Data Augumentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ImageGenerated from image </t>
+  </si>
+  <si>
+    <t>Keras API</t>
+  </si>
+  <si>
+    <t>keras model on top of pretrain model -- imagenet ( resnet50, vgg, xception)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1856,9 +1903,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F63"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="41" style="3" customWidth="1"/>
@@ -1869,7 +1916,7 @@
     <col min="7" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1883,7 +1930,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="90">
+    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45981</v>
       </c>
@@ -1894,7 +1941,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="144">
+    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45982</v>
       </c>
@@ -1905,7 +1952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="72">
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45985</v>
       </c>
@@ -1916,7 +1963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="72">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45986</v>
       </c>
@@ -1927,7 +1974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="243" customHeight="1">
+    <row r="6" spans="1:6" ht="243" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45987</v>
       </c>
@@ -1938,7 +1985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="108">
+    <row r="7" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45988</v>
       </c>
@@ -1949,7 +1996,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="126">
+    <row r="8" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>46019</v>
       </c>
@@ -1960,7 +2007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="202.2" customHeight="1">
+    <row r="9" spans="1:6" ht="202.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45992</v>
       </c>
@@ -1971,7 +2018,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="144">
+    <row r="10" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45993</v>
       </c>
@@ -1982,7 +2029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="108">
+    <row r="11" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45994</v>
       </c>
@@ -1993,7 +2040,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="220.2" customHeight="1">
+    <row r="12" spans="1:6" ht="220.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>46000</v>
       </c>
@@ -2004,7 +2051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="126">
+    <row r="13" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>46001</v>
       </c>
@@ -2015,7 +2062,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="126">
+    <row r="14" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>46002</v>
       </c>
@@ -2026,7 +2073,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="72">
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>46003</v>
       </c>
@@ -2037,7 +2084,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="108">
+    <row r="16" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>46006</v>
       </c>
@@ -2048,7 +2095,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="126">
+    <row r="17" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>46007</v>
       </c>
@@ -2059,7 +2106,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="54">
+    <row r="18" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>46008</v>
       </c>
@@ -2070,7 +2117,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="90">
+    <row r="19" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>46009</v>
       </c>
@@ -2081,7 +2128,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="144">
+    <row r="20" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>46010</v>
       </c>
@@ -2092,7 +2139,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>46012</v>
       </c>
@@ -2103,7 +2150,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="144">
+    <row r="22" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>46013</v>
       </c>
@@ -2114,7 +2161,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="90">
+    <row r="23" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>46014</v>
       </c>
@@ -2125,7 +2172,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="150" customHeight="1">
+    <row r="24" spans="1:3" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>46015</v>
       </c>
@@ -2136,7 +2183,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="118.2" customHeight="1">
+    <row r="25" spans="1:3" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>46017</v>
       </c>
@@ -2147,7 +2194,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="166.2" customHeight="1">
+    <row r="26" spans="1:3" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>46018</v>
       </c>
@@ -2158,7 +2205,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="72">
+    <row r="27" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>46020</v>
       </c>
@@ -2169,7 +2216,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="126">
+    <row r="28" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>186</v>
       </c>
@@ -2180,7 +2227,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="90.6" customHeight="1">
+    <row r="29" spans="1:3" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>200</v>
       </c>
@@ -2191,7 +2238,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="90">
+    <row r="30" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>46027</v>
       </c>
@@ -2202,7 +2249,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="180">
+    <row r="31" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>46028</v>
       </c>
@@ -2213,7 +2260,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="126">
+    <row r="32" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>46029</v>
       </c>
@@ -2224,7 +2271,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="72">
+    <row r="33" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>46030</v>
       </c>
@@ -2235,7 +2282,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="216.6" customHeight="1">
+    <row r="34" spans="1:3" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>46031</v>
       </c>
@@ -2246,7 +2293,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="126">
+    <row r="35" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>46032</v>
       </c>
@@ -2257,7 +2304,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="168" customHeight="1">
+    <row r="36" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>46034</v>
       </c>
@@ -2268,7 +2315,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="108">
+    <row r="37" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>46041</v>
       </c>
@@ -2279,7 +2326,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="144">
+    <row r="38" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>46042</v>
       </c>
@@ -2290,7 +2337,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="90">
+    <row r="39" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>46043</v>
       </c>
@@ -2301,7 +2348,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="108">
+    <row r="40" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>46044</v>
       </c>
@@ -2312,7 +2359,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="108">
+    <row r="41" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>46045</v>
       </c>
@@ -2323,7 +2370,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="126">
+    <row r="42" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>46046</v>
       </c>
@@ -2334,7 +2381,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="72">
+    <row r="43" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>46048</v>
       </c>
@@ -2345,7 +2392,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="126">
+    <row r="44" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>46049</v>
       </c>
@@ -2356,7 +2403,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="144">
+    <row r="45" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>46050</v>
       </c>
@@ -2367,7 +2414,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="162">
+    <row r="46" spans="1:3" ht="162" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>46051</v>
       </c>
@@ -2378,7 +2425,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="144">
+    <row r="47" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>46052</v>
       </c>
@@ -2389,7 +2436,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="72">
+    <row r="48" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>46055</v>
       </c>
@@ -2400,7 +2447,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="144">
+    <row r="49" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>46056</v>
       </c>
@@ -2411,7 +2458,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="108">
+    <row r="50" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>46057</v>
       </c>
@@ -2422,7 +2469,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="72">
+    <row r="51" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>46058</v>
       </c>
@@ -2433,7 +2480,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="162">
+    <row r="52" spans="1:3" ht="162" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>46059</v>
       </c>
@@ -2444,7 +2491,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="72">
+    <row r="53" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>46060</v>
       </c>
@@ -2455,7 +2502,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="108">
+    <row r="54" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>46062</v>
       </c>
@@ -2466,7 +2513,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="54">
+    <row r="55" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>46063</v>
       </c>
@@ -2477,7 +2524,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="72">
+    <row r="56" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>46064</v>
       </c>
@@ -2488,7 +2535,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="54">
+    <row r="57" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>46065</v>
       </c>
@@ -2499,7 +2546,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="36">
+    <row r="58" spans="1:3" ht="36" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>46066</v>
       </c>
@@ -2510,7 +2557,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="216">
+    <row r="59" spans="1:3" ht="216" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>46069</v>
       </c>
@@ -2521,9 +2568,42 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>46070</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+      <c r="A61" s="11">
+        <v>46071</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+      <c r="A62" s="11">
+        <v>46072</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="11">
+        <v>46076</v>
       </c>
     </row>
   </sheetData>
@@ -2533,14 +2613,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K280"/>
-  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="84.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="82.109375" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -2551,7 +2631,7 @@
     <col min="12" max="16384" width="13.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2586,7 +2666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2606,7 +2686,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="62.4">
+    <row r="3" spans="1:11" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2626,7 +2706,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2646,7 +2726,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="31.2">
+    <row r="5" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2666,7 +2746,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2686,7 +2766,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2706,7 +2786,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2726,7 +2806,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2746,7 +2826,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2766,7 +2846,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -2786,7 +2866,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="31.2">
+    <row r="12" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2806,7 +2886,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -2826,7 +2906,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="46.8">
+    <row r="14" spans="1:11" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -2846,7 +2926,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -2866,7 +2946,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -2886,7 +2966,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -2906,7 +2986,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -2926,7 +3006,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -2946,7 +3026,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -2966,7 +3046,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -2986,7 +3066,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="31.2">
+    <row r="22" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -3008,7 +3088,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -3028,7 +3108,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -3048,7 +3128,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -3068,7 +3148,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -3090,7 +3170,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -3112,7 +3192,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -3134,7 +3214,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -3154,7 +3234,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -3174,7 +3254,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -3196,7 +3276,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -3216,7 +3296,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -3236,7 +3316,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -3258,7 +3338,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -3278,7 +3358,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>35</v>
       </c>
@@ -3298,7 +3378,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" ht="31.2">
+    <row r="37" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -3318,7 +3398,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>37</v>
       </c>
@@ -3338,7 +3418,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -3358,7 +3438,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>39</v>
       </c>
@@ -3378,7 +3458,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -3398,7 +3478,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>41</v>
       </c>
@@ -3418,7 +3498,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>42</v>
       </c>
@@ -3438,7 +3518,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" ht="62.4">
+    <row r="44" spans="1:10" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>278</v>
       </c>
@@ -3458,7 +3538,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" ht="140.4">
+    <row r="45" spans="1:10" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>281</v>
       </c>
@@ -3478,7 +3558,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>61</v>
       </c>
@@ -3492,7 +3572,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>62</v>
       </c>
@@ -3512,7 +3592,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>63</v>
       </c>
@@ -3532,7 +3612,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>64</v>
       </c>
@@ -3552,7 +3632,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>65</v>
       </c>
@@ -3572,7 +3652,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>66</v>
       </c>
@@ -3592,7 +3672,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>67</v>
       </c>
@@ -3612,7 +3692,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>68</v>
       </c>
@@ -3632,7 +3712,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>69</v>
       </c>
@@ -3652,7 +3732,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>70</v>
       </c>
@@ -3672,7 +3752,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>71</v>
       </c>
@@ -3692,7 +3772,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>72</v>
       </c>
@@ -3712,7 +3792,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>73</v>
       </c>
@@ -3732,7 +3812,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>74</v>
       </c>
@@ -3752,7 +3832,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>75</v>
       </c>
@@ -3772,7 +3852,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>76</v>
       </c>
@@ -3792,11 +3872,19 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>77</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="B62" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>336</v>
+      </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
@@ -3804,8 +3892,19 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10">
-      <c r="D63" s="6"/>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>78</v>
+      </c>
+      <c r="B63" s="10">
+        <v>46076</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>339</v>
+      </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
@@ -3813,8 +3912,19 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10">
-      <c r="D64" s="6"/>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="9">
+        <v>79</v>
+      </c>
+      <c r="B64" s="10">
+        <v>46076</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>341</v>
+      </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
@@ -3822,7 +3932,8 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="4:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -3831,7 +3942,7 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" spans="4:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -3840,7 +3951,7 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="4:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -3849,7 +3960,7 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" spans="4:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -3858,7 +3969,7 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="4:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -3867,7 +3978,7 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" spans="4:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -3876,7 +3987,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="4:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -3885,7 +3996,7 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" spans="4:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -3894,7 +4005,7 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" spans="4:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -3903,7 +4014,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="4:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -3912,7 +4023,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" spans="4:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -3921,7 +4032,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="4:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -3930,7 +4041,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="4:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -3939,7 +4050,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
     </row>
-    <row r="78" spans="4:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -3948,7 +4059,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" spans="4:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -3957,7 +4068,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" spans="4:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -3966,7 +4077,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="4:10">
+    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -3975,7 +4086,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" spans="4:10">
+    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -3984,7 +4095,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="4:10">
+    <row r="83" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -3993,7 +4104,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" spans="4:10">
+    <row r="84" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4002,7 +4113,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="4:10">
+    <row r="85" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4011,7 +4122,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="4:10">
+    <row r="86" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -4020,7 +4131,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" spans="4:10">
+    <row r="87" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -4029,7 +4140,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
     </row>
-    <row r="88" spans="4:10">
+    <row r="88" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4038,7 +4149,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="4:10">
+    <row r="89" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4047,7 +4158,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" spans="4:10">
+    <row r="90" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4056,7 +4167,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="4:10">
+    <row r="91" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -4065,7 +4176,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" spans="4:10">
+    <row r="92" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -4074,7 +4185,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="4:10">
+    <row r="93" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4083,7 +4194,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" spans="4:10">
+    <row r="94" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4092,7 +4203,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="4:10">
+    <row r="95" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4101,7 +4212,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
     </row>
-    <row r="96" spans="4:10">
+    <row r="96" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -4110,7 +4221,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" spans="4:10">
+    <row r="97" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -4119,7 +4230,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
     </row>
-    <row r="98" spans="4:10">
+    <row r="98" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4128,7 +4239,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" spans="4:10">
+    <row r="99" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4137,7 +4248,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
     </row>
-    <row r="100" spans="4:10">
+    <row r="100" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -4146,7 +4257,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" spans="4:10">
+    <row r="101" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -4155,7 +4266,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
     </row>
-    <row r="102" spans="4:10">
+    <row r="102" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -4164,7 +4275,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" spans="4:10">
+    <row r="103" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -4173,7 +4284,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
     </row>
-    <row r="104" spans="4:10">
+    <row r="104" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -4182,7 +4293,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="4:10">
+    <row r="105" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -4191,7 +4302,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
     </row>
-    <row r="106" spans="4:10">
+    <row r="106" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4200,7 +4311,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" spans="4:10">
+    <row r="107" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4209,7 +4320,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
     </row>
-    <row r="108" spans="4:10">
+    <row r="108" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4218,7 +4329,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="4:10">
+    <row r="109" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4227,7 +4338,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
     </row>
-    <row r="110" spans="4:10">
+    <row r="110" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4236,7 +4347,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" spans="4:10">
+    <row r="111" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -4245,7 +4356,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
     </row>
-    <row r="112" spans="4:10">
+    <row r="112" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -4254,7 +4365,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" spans="4:10">
+    <row r="113" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4263,7 +4374,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
     </row>
-    <row r="114" spans="4:10">
+    <row r="114" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -4272,7 +4383,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" spans="4:10">
+    <row r="115" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4281,7 +4392,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
     </row>
-    <row r="116" spans="4:10">
+    <row r="116" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -4290,7 +4401,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" spans="4:10">
+    <row r="117" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4299,7 +4410,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
     </row>
-    <row r="118" spans="4:10">
+    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -4308,7 +4419,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" spans="4:10">
+    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -4317,7 +4428,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
     </row>
-    <row r="120" spans="4:10">
+    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -4326,7 +4437,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" spans="4:10">
+    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4335,7 +4446,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
     </row>
-    <row r="122" spans="4:10">
+    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4344,7 +4455,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" spans="4:10">
+    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4353,7 +4464,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
     </row>
-    <row r="124" spans="4:10">
+    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -4362,7 +4473,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" spans="4:10">
+    <row r="125" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4371,7 +4482,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" spans="4:10">
+    <row r="126" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4380,7 +4491,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="4:10">
+    <row r="127" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4389,7 +4500,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
     </row>
-    <row r="128" spans="4:10">
+    <row r="128" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4398,7 +4509,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
     </row>
-    <row r="129" spans="4:10">
+    <row r="129" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4407,7 +4518,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
     </row>
-    <row r="130" spans="4:10">
+    <row r="130" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4416,7 +4527,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
     </row>
-    <row r="131" spans="4:10">
+    <row r="131" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4425,7 +4536,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
     </row>
-    <row r="132" spans="4:10">
+    <row r="132" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4434,7 +4545,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
     </row>
-    <row r="133" spans="4:10">
+    <row r="133" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4443,7 +4554,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
     </row>
-    <row r="134" spans="4:10">
+    <row r="134" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -4452,7 +4563,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
     </row>
-    <row r="135" spans="4:10">
+    <row r="135" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4461,7 +4572,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
     </row>
-    <row r="136" spans="4:10">
+    <row r="136" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -4470,7 +4581,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
     </row>
-    <row r="137" spans="4:10">
+    <row r="137" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4479,7 +4590,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
     </row>
-    <row r="138" spans="4:10">
+    <row r="138" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -4488,7 +4599,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
     </row>
-    <row r="139" spans="4:10">
+    <row r="139" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4497,7 +4608,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
     </row>
-    <row r="140" spans="4:10">
+    <row r="140" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4506,7 +4617,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
     </row>
-    <row r="141" spans="4:10">
+    <row r="141" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4515,7 +4626,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
     </row>
-    <row r="142" spans="4:10">
+    <row r="142" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -4524,7 +4635,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
     </row>
-    <row r="143" spans="4:10">
+    <row r="143" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4533,7 +4644,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
     </row>
-    <row r="144" spans="4:10">
+    <row r="144" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4542,7 +4653,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
     </row>
-    <row r="145" spans="4:10">
+    <row r="145" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4551,7 +4662,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
     </row>
-    <row r="146" spans="4:10">
+    <row r="146" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4560,7 +4671,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
     </row>
-    <row r="147" spans="4:10">
+    <row r="147" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4569,7 +4680,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
     </row>
-    <row r="148" spans="4:10">
+    <row r="148" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4578,7 +4689,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
     </row>
-    <row r="149" spans="4:10">
+    <row r="149" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -4587,7 +4698,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
     </row>
-    <row r="150" spans="4:10">
+    <row r="150" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -4596,7 +4707,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
     </row>
-    <row r="151" spans="4:10">
+    <row r="151" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
@@ -4605,7 +4716,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
     </row>
-    <row r="152" spans="4:10">
+    <row r="152" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4614,7 +4725,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
     </row>
-    <row r="153" spans="4:10">
+    <row r="153" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
@@ -4623,7 +4734,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
     </row>
-    <row r="154" spans="4:10">
+    <row r="154" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4632,7 +4743,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
     </row>
-    <row r="155" spans="4:10">
+    <row r="155" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4641,7 +4752,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
     </row>
-    <row r="156" spans="4:10">
+    <row r="156" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -4650,7 +4761,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
     </row>
-    <row r="157" spans="4:10">
+    <row r="157" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
@@ -4659,7 +4770,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
     </row>
-    <row r="158" spans="4:10">
+    <row r="158" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
@@ -4668,7 +4779,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
     </row>
-    <row r="159" spans="4:10">
+    <row r="159" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
       <c r="F159" s="6"/>
@@ -4677,7 +4788,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
     </row>
-    <row r="160" spans="4:10">
+    <row r="160" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
       <c r="F160" s="6"/>
@@ -4686,7 +4797,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
     </row>
-    <row r="161" spans="4:10">
+    <row r="161" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
@@ -4695,7 +4806,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
     </row>
-    <row r="162" spans="4:10">
+    <row r="162" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
@@ -4704,7 +4815,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
     </row>
-    <row r="163" spans="4:10">
+    <row r="163" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
@@ -4713,7 +4824,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
     </row>
-    <row r="164" spans="4:10">
+    <row r="164" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
@@ -4722,7 +4833,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
     </row>
-    <row r="165" spans="4:10">
+    <row r="165" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
@@ -4731,7 +4842,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
     </row>
-    <row r="166" spans="4:10">
+    <row r="166" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -4740,7 +4851,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
     </row>
-    <row r="167" spans="4:10">
+    <row r="167" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
@@ -4749,7 +4860,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
     </row>
-    <row r="168" spans="4:10">
+    <row r="168" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -4758,7 +4869,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
     </row>
-    <row r="169" spans="4:10">
+    <row r="169" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
@@ -4767,7 +4878,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
     </row>
-    <row r="170" spans="4:10">
+    <row r="170" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
@@ -4776,7 +4887,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" spans="4:10">
+    <row r="171" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
@@ -4785,7 +4896,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" spans="4:10">
+    <row r="172" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
@@ -4794,7 +4905,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
     </row>
-    <row r="173" spans="4:10">
+    <row r="173" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
@@ -4803,7 +4914,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
     </row>
-    <row r="174" spans="4:10">
+    <row r="174" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
@@ -4812,7 +4923,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
     </row>
-    <row r="175" spans="4:10">
+    <row r="175" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
@@ -4821,7 +4932,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
     </row>
-    <row r="176" spans="4:10">
+    <row r="176" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
@@ -4830,7 +4941,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
     </row>
-    <row r="177" spans="4:10">
+    <row r="177" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
@@ -4839,7 +4950,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
     </row>
-    <row r="178" spans="4:10">
+    <row r="178" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
@@ -4848,7 +4959,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
     </row>
-    <row r="179" spans="4:10">
+    <row r="179" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
@@ -4857,7 +4968,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
     </row>
-    <row r="180" spans="4:10">
+    <row r="180" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
@@ -4866,7 +4977,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
     </row>
-    <row r="181" spans="4:10">
+    <row r="181" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
@@ -4875,7 +4986,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
     </row>
-    <row r="182" spans="4:10">
+    <row r="182" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
@@ -4884,7 +4995,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
     </row>
-    <row r="183" spans="4:10">
+    <row r="183" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
@@ -4893,7 +5004,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
     </row>
-    <row r="184" spans="4:10">
+    <row r="184" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
@@ -4902,7 +5013,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
     </row>
-    <row r="185" spans="4:10">
+    <row r="185" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
@@ -4911,7 +5022,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
     </row>
-    <row r="186" spans="4:10">
+    <row r="186" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
@@ -4920,7 +5031,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
     </row>
-    <row r="187" spans="4:10">
+    <row r="187" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
@@ -4929,7 +5040,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
     </row>
-    <row r="188" spans="4:10">
+    <row r="188" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
@@ -4938,7 +5049,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
     </row>
-    <row r="189" spans="4:10">
+    <row r="189" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
@@ -4947,7 +5058,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
     </row>
-    <row r="190" spans="4:10">
+    <row r="190" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
@@ -4956,7 +5067,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
     </row>
-    <row r="191" spans="4:10">
+    <row r="191" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
@@ -4965,7 +5076,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
     </row>
-    <row r="192" spans="4:10">
+    <row r="192" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
@@ -4974,7 +5085,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
     </row>
-    <row r="193" spans="4:10">
+    <row r="193" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
@@ -4983,7 +5094,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
     </row>
-    <row r="194" spans="4:10">
+    <row r="194" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
@@ -4992,7 +5103,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
     </row>
-    <row r="195" spans="4:10">
+    <row r="195" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
@@ -5001,7 +5112,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
     </row>
-    <row r="196" spans="4:10">
+    <row r="196" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
@@ -5010,7 +5121,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
     </row>
-    <row r="197" spans="4:10">
+    <row r="197" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
       <c r="F197" s="6"/>
@@ -5019,7 +5130,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="6"/>
     </row>
-    <row r="198" spans="4:10">
+    <row r="198" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
       <c r="F198" s="6"/>
@@ -5028,7 +5139,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="6"/>
     </row>
-    <row r="199" spans="4:10">
+    <row r="199" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
@@ -5037,7 +5148,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="6"/>
     </row>
-    <row r="200" spans="4:10">
+    <row r="200" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
@@ -5046,7 +5157,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="6"/>
     </row>
-    <row r="201" spans="4:10">
+    <row r="201" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
@@ -5055,7 +5166,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="6"/>
     </row>
-    <row r="202" spans="4:10">
+    <row r="202" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
@@ -5064,7 +5175,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="6"/>
     </row>
-    <row r="203" spans="4:10">
+    <row r="203" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
@@ -5073,7 +5184,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="6"/>
     </row>
-    <row r="204" spans="4:10">
+    <row r="204" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
@@ -5082,7 +5193,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="6"/>
     </row>
-    <row r="205" spans="4:10">
+    <row r="205" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
@@ -5091,7 +5202,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="6"/>
     </row>
-    <row r="206" spans="4:10">
+    <row r="206" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
@@ -5100,7 +5211,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="6"/>
     </row>
-    <row r="207" spans="4:10">
+    <row r="207" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
@@ -5109,7 +5220,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="6"/>
     </row>
-    <row r="208" spans="4:10">
+    <row r="208" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
@@ -5118,7 +5229,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="6"/>
     </row>
-    <row r="209" spans="4:10">
+    <row r="209" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
@@ -5127,7 +5238,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="6"/>
     </row>
-    <row r="210" spans="4:10">
+    <row r="210" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
@@ -5136,7 +5247,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
     </row>
-    <row r="211" spans="4:10">
+    <row r="211" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
@@ -5145,7 +5256,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="6"/>
     </row>
-    <row r="212" spans="4:10">
+    <row r="212" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
@@ -5154,7 +5265,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
     </row>
-    <row r="213" spans="4:10">
+    <row r="213" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
@@ -5163,7 +5274,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
     </row>
-    <row r="214" spans="4:10">
+    <row r="214" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
@@ -5172,7 +5283,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
     </row>
-    <row r="215" spans="4:10">
+    <row r="215" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
@@ -5181,7 +5292,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
     </row>
-    <row r="216" spans="4:10">
+    <row r="216" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
@@ -5190,7 +5301,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
     </row>
-    <row r="217" spans="4:10">
+    <row r="217" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
@@ -5199,7 +5310,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
     </row>
-    <row r="218" spans="4:10">
+    <row r="218" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
@@ -5208,7 +5319,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
     </row>
-    <row r="219" spans="4:10">
+    <row r="219" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
@@ -5217,7 +5328,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
     </row>
-    <row r="220" spans="4:10">
+    <row r="220" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -5226,7 +5337,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="6"/>
     </row>
-    <row r="221" spans="4:10">
+    <row r="221" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
@@ -5235,7 +5346,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="6"/>
     </row>
-    <row r="222" spans="4:10">
+    <row r="222" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
@@ -5244,7 +5355,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="6"/>
     </row>
-    <row r="223" spans="4:10">
+    <row r="223" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
@@ -5253,7 +5364,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="6"/>
     </row>
-    <row r="224" spans="4:10">
+    <row r="224" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
@@ -5262,7 +5373,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="6"/>
     </row>
-    <row r="225" spans="4:10">
+    <row r="225" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
@@ -5271,7 +5382,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="6"/>
     </row>
-    <row r="226" spans="4:10">
+    <row r="226" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
@@ -5280,7 +5391,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="6"/>
     </row>
-    <row r="227" spans="4:10">
+    <row r="227" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
@@ -5289,7 +5400,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="6"/>
     </row>
-    <row r="228" spans="4:10">
+    <row r="228" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
@@ -5298,7 +5409,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="6"/>
     </row>
-    <row r="229" spans="4:10">
+    <row r="229" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
@@ -5307,7 +5418,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="6"/>
     </row>
-    <row r="230" spans="4:10">
+    <row r="230" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
@@ -5316,7 +5427,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="6"/>
     </row>
-    <row r="231" spans="4:10">
+    <row r="231" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
@@ -5325,7 +5436,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="6"/>
     </row>
-    <row r="232" spans="4:10">
+    <row r="232" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
@@ -5334,7 +5445,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="6"/>
     </row>
-    <row r="233" spans="4:10">
+    <row r="233" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
@@ -5343,7 +5454,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="6"/>
     </row>
-    <row r="234" spans="4:10">
+    <row r="234" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
@@ -5352,7 +5463,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="6"/>
     </row>
-    <row r="235" spans="4:10">
+    <row r="235" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
@@ -5361,7 +5472,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="6"/>
     </row>
-    <row r="236" spans="4:10">
+    <row r="236" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
@@ -5370,7 +5481,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="6"/>
     </row>
-    <row r="237" spans="4:10">
+    <row r="237" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
@@ -5379,7 +5490,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="6"/>
     </row>
-    <row r="238" spans="4:10">
+    <row r="238" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
@@ -5388,7 +5499,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="6"/>
     </row>
-    <row r="239" spans="4:10">
+    <row r="239" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -5397,7 +5508,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="6"/>
     </row>
-    <row r="240" spans="4:10">
+    <row r="240" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -5406,7 +5517,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="6"/>
     </row>
-    <row r="241" spans="4:10">
+    <row r="241" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -5415,7 +5526,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="6"/>
     </row>
-    <row r="242" spans="4:10">
+    <row r="242" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -5424,7 +5535,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="6"/>
     </row>
-    <row r="243" spans="4:10">
+    <row r="243" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -5433,7 +5544,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="6"/>
     </row>
-    <row r="244" spans="4:10">
+    <row r="244" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -5442,7 +5553,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="6"/>
     </row>
-    <row r="245" spans="4:10">
+    <row r="245" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -5451,7 +5562,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="6"/>
     </row>
-    <row r="246" spans="4:10">
+    <row r="246" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -5460,7 +5571,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="6"/>
     </row>
-    <row r="247" spans="4:10">
+    <row r="247" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -5469,7 +5580,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="6"/>
     </row>
-    <row r="248" spans="4:10">
+    <row r="248" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -5478,7 +5589,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
     </row>
-    <row r="249" spans="4:10">
+    <row r="249" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -5487,7 +5598,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
     </row>
-    <row r="250" spans="4:10">
+    <row r="250" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -5496,7 +5607,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="6"/>
     </row>
-    <row r="251" spans="4:10">
+    <row r="251" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -5505,7 +5616,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="6"/>
     </row>
-    <row r="252" spans="4:10">
+    <row r="252" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -5514,7 +5625,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="6"/>
     </row>
-    <row r="253" spans="4:10">
+    <row r="253" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -5523,7 +5634,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="6"/>
     </row>
-    <row r="254" spans="4:10">
+    <row r="254" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -5532,7 +5643,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="6"/>
     </row>
-    <row r="255" spans="4:10">
+    <row r="255" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -5541,7 +5652,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
     </row>
-    <row r="256" spans="4:10">
+    <row r="256" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -5550,7 +5661,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
     </row>
-    <row r="257" spans="4:10">
+    <row r="257" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -5559,7 +5670,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
     </row>
-    <row r="258" spans="4:10">
+    <row r="258" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -5568,7 +5679,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="6"/>
     </row>
-    <row r="259" spans="4:10">
+    <row r="259" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -5577,7 +5688,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="6"/>
     </row>
-    <row r="260" spans="4:10">
+    <row r="260" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -5586,7 +5697,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="6"/>
     </row>
-    <row r="261" spans="4:10">
+    <row r="261" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -5595,7 +5706,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="6"/>
     </row>
-    <row r="262" spans="4:10">
+    <row r="262" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -5604,7 +5715,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="6"/>
     </row>
-    <row r="263" spans="4:10">
+    <row r="263" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
@@ -5613,7 +5724,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="6"/>
     </row>
-    <row r="264" spans="4:10">
+    <row r="264" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
@@ -5622,7 +5733,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="6"/>
     </row>
-    <row r="265" spans="4:10">
+    <row r="265" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
@@ -5631,7 +5742,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
     </row>
-    <row r="266" spans="4:10">
+    <row r="266" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
@@ -5640,7 +5751,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="6"/>
     </row>
-    <row r="267" spans="4:10">
+    <row r="267" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
@@ -5649,7 +5760,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="6"/>
     </row>
-    <row r="268" spans="4:10">
+    <row r="268" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
@@ -5658,7 +5769,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="6"/>
     </row>
-    <row r="269" spans="4:10">
+    <row r="269" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
@@ -5667,7 +5778,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="6"/>
     </row>
-    <row r="270" spans="4:10">
+    <row r="270" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
@@ -5676,7 +5787,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="6"/>
     </row>
-    <row r="271" spans="4:10">
+    <row r="271" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
@@ -5685,7 +5796,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="6"/>
     </row>
-    <row r="272" spans="4:10">
+    <row r="272" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
@@ -5694,7 +5805,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="6"/>
     </row>
-    <row r="273" spans="4:10">
+    <row r="273" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
@@ -5703,7 +5814,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="6"/>
     </row>
-    <row r="274" spans="4:10">
+    <row r="274" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
@@ -5712,7 +5823,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="6"/>
     </row>
-    <row r="275" spans="4:10">
+    <row r="275" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
@@ -5721,7 +5832,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="6"/>
     </row>
-    <row r="276" spans="4:10">
+    <row r="276" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
@@ -5730,7 +5841,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="6"/>
     </row>
-    <row r="277" spans="4:10">
+    <row r="277" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
@@ -5739,7 +5850,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="6"/>
     </row>
-    <row r="278" spans="4:10">
+    <row r="278" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
@@ -5748,7 +5859,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="6"/>
     </row>
-    <row r="279" spans="4:10">
+    <row r="279" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
@@ -5757,7 +5868,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="6"/>
     </row>
-    <row r="280" spans="4:10">
+    <row r="280" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
@@ -5773,9 +5884,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:N53"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
     <col min="3" max="3" width="10.109375" style="13" customWidth="1"/>
@@ -5787,12 +5898,12 @@
     <col min="10" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10">
+    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F3" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="3:10">
+    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C4" s="17" t="s">
         <v>78</v>
       </c>
@@ -5816,7 +5927,7 @@
       </c>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" s="14" t="s">
         <v>85</v>
       </c>
@@ -5834,7 +5945,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="15"/>
     </row>
-    <row r="6" spans="3:10">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="14" t="s">
         <v>88</v>
       </c>
@@ -5854,12 +5965,12 @@
       <c r="I6" s="17"/>
       <c r="J6" s="15"/>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F10" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" s="17" t="s">
         <v>78</v>
       </c>
@@ -5882,7 +5993,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" s="14" t="s">
         <v>85</v>
       </c>
@@ -5905,7 +6016,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>88</v>
       </c>
@@ -5928,12 +6039,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" s="18" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>141</v>
       </c>
@@ -5975,7 +6086,7 @@
       </c>
       <c r="N17" s="19"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
         <v>78</v>
       </c>
@@ -6019,7 +6130,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>134</v>
       </c>
@@ -6061,7 +6172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>153</v>
       </c>
@@ -6101,12 +6212,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C23" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
         <v>143</v>
       </c>
@@ -6138,7 +6249,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B25" s="17" t="s">
         <v>126</v>
       </c>
@@ -6170,7 +6281,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>91</v>
       </c>
@@ -6200,7 +6311,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>154</v>
       </c>
@@ -6228,12 +6339,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27.6">
+    <row r="29" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
       <c r="F29" s="22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>164</v>
       </c>
@@ -6259,7 +6370,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B31" s="14">
         <v>13</v>
       </c>
@@ -6285,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>15</v>
       </c>
@@ -6311,7 +6422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>165</v>
       </c>
@@ -6340,7 +6451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>166</v>
       </c>
@@ -6369,7 +6480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>167</v>
       </c>
@@ -6398,7 +6509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B36" s="17">
         <v>21.4</v>
       </c>
@@ -6424,7 +6535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B37" s="14">
         <v>35</v>
       </c>
@@ -6450,7 +6561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B38" s="17">
         <v>35</v>
       </c>
@@ -6476,7 +6587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -6499,7 +6610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B40" s="14">
         <v>35</v>
       </c>
@@ -6522,12 +6633,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F42" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D43" s="16" t="s">
         <v>173</v>
       </c>
@@ -6538,7 +6649,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D44" s="16" t="s">
         <v>174</v>
       </c>
@@ -6549,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D45" s="16" t="s">
         <v>175</v>
       </c>
@@ -6560,7 +6671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F46" s="17" t="s">
         <v>176</v>
       </c>
@@ -6568,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F47" s="14" t="s">
         <v>171</v>
       </c>
@@ -6576,7 +6687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F48" s="14" t="s">
         <v>170</v>
       </c>
@@ -6584,7 +6695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="6:7">
+    <row r="49" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F49" s="14" t="s">
         <v>171</v>
       </c>
@@ -6592,7 +6703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="6:7">
+    <row r="50" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F50" s="17" t="s">
         <v>170</v>
       </c>
@@ -6600,7 +6711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="6:7">
+    <row r="51" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F51" s="14" t="s">
         <v>169</v>
       </c>
@@ -6608,7 +6719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="6:7">
+    <row r="52" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F52" s="14" t="s">
         <v>180</v>
       </c>
@@ -6616,7 +6727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="6:7">
+    <row r="53" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F53" s="14" t="s">
         <v>181</v>
       </c>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7B7F7E-E73B-4B81-9ED9-6F8DBA0FE303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9B358-8679-41EB-B7BF-B6D80CC090D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="350">
   <si>
     <t>Date</t>
   </si>
@@ -1358,32 +1358,61 @@
     <t>happy or sad classification</t>
   </si>
   <si>
-    <t xml:space="preserve">we have few images | train test validation 
+    <t>Data Augumentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ImageGenerated from image </t>
+  </si>
+  <si>
+    <t>Keras API</t>
+  </si>
+  <si>
+    <t>keras model on top of pretrain model -- imagenet ( resnet50, vgg, xception)</t>
+  </si>
+  <si>
+    <t>we have few images | train test validation 
 train &amp; validation -- we create 2 folder happy face &amp; sad faces 
 testing -- pass few random images in both folder 
 image shpas are happening how image are convered to array
 .flow_from_directory (train &amp; test) rms prop optimizer loss function -- binarycross entropy activation relu,
- conv2d, maxpool2d, flatten &amp; integrated to gradio application to detec
-</t>
-  </si>
-  <si>
-    <t>Data Augumentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ImageGenerated from image </t>
-  </si>
-  <si>
-    <t>Keras API</t>
-  </si>
-  <si>
-    <t>keras model on top of pretrain model -- imagenet ( resnet50, vgg, xception)</t>
+ conv2d, maxpool2d, flatten &amp; integrated to gradio application to detect</t>
+  </si>
+  <si>
+    <t>keras pretreained model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resnet 50, resnet 50v2, enasnet, vgg16, vgg19
+imagenet -- pretrained weights (dataset which converted to yaml file ) 
+data augumentation we are using image data generator 
+we built how from 1image we created multipled generated images using help of  keras image datagenerator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">poc-1 : read, write, show image using opencv | face detection using haar casscade classifier | face &amp; eye detection using opencv | pedestistian detection | car detection | only video lines detection using opencv </t>
+  </si>
+  <si>
+    <t>80 - 85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opencv  &amp; haar cascade </t>
+  </si>
+  <si>
+    <t>opencv-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open cv &amp; haar cascade classifier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">poc-1 : read, write, show image using opencv | face detection using haar casscade classifier | face &amp; eye detection using opencv | pedestistian detection | car detection | only video lines detection using opencv 
+videocapture(0) -- immediaty it will open system webcamer-- it will detect your face 
+videocapture(videopath ) -- it will detect video path 
+video capture(1) -- inf any camera outside to the system then it will detect </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1904,8 +1933,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F65"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="41" style="3" customWidth="1"/>
@@ -1916,7 +1945,7 @@
     <col min="7" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1959,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="90">
       <c r="A2" s="11">
         <v>45981</v>
       </c>
@@ -1941,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="144">
       <c r="A3" s="11">
         <v>45982</v>
       </c>
@@ -1952,7 +1981,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="72">
       <c r="A4" s="11">
         <v>45985</v>
       </c>
@@ -1963,7 +1992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="72">
       <c r="A5" s="11">
         <v>45986</v>
       </c>
@@ -1974,7 +2003,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="243" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="243" customHeight="1">
       <c r="A6" s="11">
         <v>45987</v>
       </c>
@@ -1985,7 +2014,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="108" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="108">
       <c r="A7" s="11">
         <v>45988</v>
       </c>
@@ -1996,7 +2025,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="126">
       <c r="A8" s="11">
         <v>46019</v>
       </c>
@@ -2007,7 +2036,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="202.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="202.2" customHeight="1">
       <c r="A9" s="11">
         <v>45992</v>
       </c>
@@ -2018,7 +2047,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="144" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="144">
       <c r="A10" s="11">
         <v>45993</v>
       </c>
@@ -2029,7 +2058,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="108" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="108">
       <c r="A11" s="11">
         <v>45994</v>
       </c>
@@ -2040,7 +2069,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="220.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="220.2" customHeight="1">
       <c r="A12" s="11">
         <v>46000</v>
       </c>
@@ -2051,7 +2080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="126">
       <c r="A13" s="11">
         <v>46001</v>
       </c>
@@ -2062,7 +2091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="126" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="126">
       <c r="A14" s="11">
         <v>46002</v>
       </c>
@@ -2073,7 +2102,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="72">
       <c r="A15" s="11">
         <v>46003</v>
       </c>
@@ -2084,7 +2113,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="108" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="108">
       <c r="A16" s="11">
         <v>46006</v>
       </c>
@@ -2095,7 +2124,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="126">
       <c r="A17" s="11">
         <v>46007</v>
       </c>
@@ -2106,7 +2135,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="54" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="54">
       <c r="A18" s="11">
         <v>46008</v>
       </c>
@@ -2117,7 +2146,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="90">
       <c r="A19" s="11">
         <v>46009</v>
       </c>
@@ -2128,7 +2157,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="144">
       <c r="A20" s="11">
         <v>46010</v>
       </c>
@@ -2139,7 +2168,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="11">
         <v>46012</v>
       </c>
@@ -2150,7 +2179,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="144">
       <c r="A22" s="11">
         <v>46013</v>
       </c>
@@ -2161,7 +2190,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="90">
       <c r="A23" s="11">
         <v>46014</v>
       </c>
@@ -2172,7 +2201,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="150" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="150" customHeight="1">
       <c r="A24" s="11">
         <v>46015</v>
       </c>
@@ -2183,7 +2212,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="118.2" customHeight="1">
       <c r="A25" s="11">
         <v>46017</v>
       </c>
@@ -2194,7 +2223,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="166.2" customHeight="1">
       <c r="A26" s="11">
         <v>46018</v>
       </c>
@@ -2205,7 +2234,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="72">
       <c r="A27" s="11">
         <v>46020</v>
       </c>
@@ -2216,7 +2245,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="126">
       <c r="A28" s="25" t="s">
         <v>186</v>
       </c>
@@ -2227,7 +2256,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="90.6" customHeight="1">
       <c r="A29" s="25" t="s">
         <v>200</v>
       </c>
@@ -2238,7 +2267,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="90">
       <c r="A30" s="11">
         <v>46027</v>
       </c>
@@ -2249,7 +2278,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="180">
       <c r="A31" s="11">
         <v>46028</v>
       </c>
@@ -2260,7 +2289,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="126">
       <c r="A32" s="11">
         <v>46029</v>
       </c>
@@ -2271,7 +2300,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="72">
       <c r="A33" s="11">
         <v>46030</v>
       </c>
@@ -2282,7 +2311,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="216.6" customHeight="1">
       <c r="A34" s="11">
         <v>46031</v>
       </c>
@@ -2293,7 +2322,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="126">
       <c r="A35" s="11">
         <v>46032</v>
       </c>
@@ -2304,7 +2333,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="168" customHeight="1">
       <c r="A36" s="11">
         <v>46034</v>
       </c>
@@ -2315,7 +2344,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="108">
       <c r="A37" s="11">
         <v>46041</v>
       </c>
@@ -2326,7 +2355,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="144">
       <c r="A38" s="11">
         <v>46042</v>
       </c>
@@ -2337,7 +2366,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="90">
       <c r="A39" s="11">
         <v>46043</v>
       </c>
@@ -2348,7 +2377,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="108">
       <c r="A40" s="11">
         <v>46044</v>
       </c>
@@ -2359,7 +2388,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="108">
       <c r="A41" s="11">
         <v>46045</v>
       </c>
@@ -2370,7 +2399,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="126">
       <c r="A42" s="11">
         <v>46046</v>
       </c>
@@ -2381,7 +2410,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="72">
       <c r="A43" s="11">
         <v>46048</v>
       </c>
@@ -2392,7 +2421,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="126">
       <c r="A44" s="11">
         <v>46049</v>
       </c>
@@ -2403,7 +2432,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="126">
       <c r="A45" s="11">
         <v>46050</v>
       </c>
@@ -2414,7 +2443,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="162" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="162">
       <c r="A46" s="11">
         <v>46051</v>
       </c>
@@ -2425,7 +2454,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="144">
       <c r="A47" s="11">
         <v>46052</v>
       </c>
@@ -2436,7 +2465,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="72">
       <c r="A48" s="11">
         <v>46055</v>
       </c>
@@ -2447,7 +2476,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="144">
       <c r="A49" s="11">
         <v>46056</v>
       </c>
@@ -2458,7 +2487,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="108">
       <c r="A50" s="11">
         <v>46057</v>
       </c>
@@ -2469,7 +2498,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="72">
       <c r="A51" s="11">
         <v>46058</v>
       </c>
@@ -2480,7 +2509,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="162" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="162">
       <c r="A52" s="11">
         <v>46059</v>
       </c>
@@ -2491,7 +2520,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="72">
       <c r="A53" s="11">
         <v>46060</v>
       </c>
@@ -2502,7 +2531,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="108">
       <c r="A54" s="11">
         <v>46062</v>
       </c>
@@ -2513,7 +2542,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="54" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="54">
       <c r="A55" s="11">
         <v>46063</v>
       </c>
@@ -2524,7 +2553,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="72">
       <c r="A56" s="11">
         <v>46064</v>
       </c>
@@ -2535,7 +2564,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="54" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="54">
       <c r="A57" s="11">
         <v>46065</v>
       </c>
@@ -2546,7 +2575,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="36">
       <c r="A58" s="11">
         <v>46066</v>
       </c>
@@ -2557,7 +2586,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="216" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="216">
       <c r="A59" s="11">
         <v>46069</v>
       </c>
@@ -2568,7 +2597,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="90">
       <c r="A60" s="11">
         <v>46070</v>
       </c>
@@ -2579,7 +2608,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="144" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="144">
       <c r="A61" s="11">
         <v>46071</v>
       </c>
@@ -2590,7 +2619,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="108">
       <c r="A62" s="11">
         <v>46072</v>
       </c>
@@ -2598,13 +2627,36 @@
         <v>333</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="72">
       <c r="A63" s="11">
         <v>46076</v>
       </c>
+      <c r="B63" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="90">
+      <c r="A64" s="11">
+        <v>46077</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="11">
+        <v>46078</v>
+      </c>
+      <c r="C65" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2615,7 +2667,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K280"/>
-  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
@@ -2631,7 +2683,7 @@
     <col min="12" max="16384" width="13.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2666,7 +2718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2686,7 +2738,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="62.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="62.4">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2706,7 +2758,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2726,7 +2778,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="31.2">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2746,7 +2798,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2766,7 +2818,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2786,7 +2838,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2806,7 +2858,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2826,7 +2878,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2846,7 +2898,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -2866,7 +2918,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="31.2">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2886,7 +2938,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -2906,7 +2958,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="46.8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="46.8">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -2926,7 +2978,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -2946,7 +2998,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -2966,7 +3018,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -2986,7 +3038,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -3006,7 +3058,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -3026,7 +3078,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -3046,7 +3098,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -3066,7 +3118,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="31.2">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -3088,7 +3140,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -3108,7 +3160,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -3128,7 +3180,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -3148,7 +3200,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -3170,7 +3222,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -3192,7 +3244,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -3214,7 +3266,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -3234,7 +3286,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -3254,7 +3306,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -3276,7 +3328,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -3296,7 +3348,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -3316,7 +3368,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -3338,7 +3390,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -3358,7 +3410,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="9">
         <v>35</v>
       </c>
@@ -3378,7 +3430,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="31.2">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -3398,7 +3450,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="9">
         <v>37</v>
       </c>
@@ -3418,7 +3470,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -3438,7 +3490,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="9">
         <v>39</v>
       </c>
@@ -3458,7 +3510,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -3478,7 +3530,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="9">
         <v>41</v>
       </c>
@@ -3498,7 +3550,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="9">
         <v>42</v>
       </c>
@@ -3518,7 +3570,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" ht="62.4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="62.4">
       <c r="A44" s="9" t="s">
         <v>278</v>
       </c>
@@ -3538,7 +3590,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" ht="140.4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="140.4">
       <c r="A45" s="9" t="s">
         <v>281</v>
       </c>
@@ -3558,7 +3610,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="9">
         <v>61</v>
       </c>
@@ -3572,7 +3624,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="9">
         <v>62</v>
       </c>
@@ -3592,7 +3644,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="9">
         <v>63</v>
       </c>
@@ -3612,7 +3664,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="9">
         <v>64</v>
       </c>
@@ -3632,7 +3684,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="9">
         <v>65</v>
       </c>
@@ -3652,7 +3704,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="9">
         <v>66</v>
       </c>
@@ -3672,7 +3724,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="9">
         <v>67</v>
       </c>
@@ -3692,7 +3744,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="9">
         <v>68</v>
       </c>
@@ -3712,7 +3764,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="9">
         <v>69</v>
       </c>
@@ -3732,7 +3784,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="9">
         <v>70</v>
       </c>
@@ -3752,7 +3804,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="9">
         <v>71</v>
       </c>
@@ -3772,7 +3824,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" s="9">
         <v>72</v>
       </c>
@@ -3792,7 +3844,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="9">
         <v>73</v>
       </c>
@@ -3812,7 +3864,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="9">
         <v>74</v>
       </c>
@@ -3832,7 +3884,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="9">
         <v>75</v>
       </c>
@@ -3852,7 +3904,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="9">
         <v>76</v>
       </c>
@@ -3872,7 +3924,7 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="9">
         <v>77</v>
       </c>
@@ -3892,7 +3944,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63" s="9">
         <v>78</v>
       </c>
@@ -3900,10 +3952,10 @@
         <v>46076</v>
       </c>
       <c r="C63" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>338</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>339</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -3912,7 +3964,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" s="9">
         <v>79</v>
       </c>
@@ -3920,10 +3972,10 @@
         <v>46076</v>
       </c>
       <c r="C64" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>341</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -3932,9 +3984,19 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="9"/>
-      <c r="D65" s="6"/>
+    <row r="65" spans="1:10" ht="46.8">
+      <c r="A65" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B65" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
@@ -3942,7 +4004,16 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10">
+      <c r="A66" s="9">
+        <v>86</v>
+      </c>
+      <c r="B66" s="10">
+        <v>46078</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>347</v>
+      </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -3951,7 +4022,7 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10">
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
@@ -3960,7 +4031,7 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10">
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -3969,7 +4040,7 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10">
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -3978,7 +4049,7 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10">
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -3987,7 +4058,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10">
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -3996,7 +4067,7 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -4005,7 +4076,7 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10">
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -4014,7 +4085,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10">
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -4023,7 +4094,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -4032,7 +4103,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10">
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -4041,7 +4112,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10">
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -4050,7 +4121,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10">
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -4059,7 +4130,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -4068,7 +4139,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10">
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -4077,7 +4148,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:10">
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -4086,7 +4157,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:10">
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -4095,7 +4166,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:10">
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4104,7 +4175,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:10">
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4113,7 +4184,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:10">
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4122,7 +4193,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:10">
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -4131,7 +4202,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:10">
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -4140,7 +4211,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
     </row>
-    <row r="88" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:10">
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4149,7 +4220,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:10">
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4158,7 +4229,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:10">
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4167,7 +4238,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:10">
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -4176,7 +4247,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:10">
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -4185,7 +4256,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:10">
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4194,7 +4265,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:10">
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4203,7 +4274,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:10">
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4212,7 +4283,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
     </row>
-    <row r="96" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:10">
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -4221,7 +4292,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:10">
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -4230,7 +4301,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
     </row>
-    <row r="98" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:10">
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4239,7 +4310,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:10">
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4248,7 +4319,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
     </row>
-    <row r="100" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:10">
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -4257,7 +4328,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:10">
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -4266,7 +4337,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
     </row>
-    <row r="102" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:10">
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -4275,7 +4346,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:10">
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -4284,7 +4355,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
     </row>
-    <row r="104" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:10">
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -4293,7 +4364,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:10">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -4302,7 +4373,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
     </row>
-    <row r="106" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:10">
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4311,7 +4382,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:10">
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4320,7 +4391,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
     </row>
-    <row r="108" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:10">
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4329,7 +4400,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:10">
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4338,7 +4409,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
     </row>
-    <row r="110" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:10">
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4347,7 +4418,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:10">
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -4356,7 +4427,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
     </row>
-    <row r="112" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:10">
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -4365,7 +4436,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:10">
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4374,7 +4445,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
     </row>
-    <row r="114" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:10">
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -4383,7 +4454,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:10">
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4392,7 +4463,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
     </row>
-    <row r="116" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:10">
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -4401,7 +4472,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:10">
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4410,7 +4481,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
     </row>
-    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:10">
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -4419,7 +4490,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:10">
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -4428,7 +4499,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
     </row>
-    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:10">
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -4437,7 +4508,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:10">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4446,7 +4517,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
     </row>
-    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:10">
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4455,7 +4526,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:10">
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4464,7 +4535,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
     </row>
-    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:10">
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -4473,7 +4544,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:10">
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4482,7 +4553,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:10">
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4491,7 +4562,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:10">
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4500,7 +4571,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
     </row>
-    <row r="128" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:10">
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4509,7 +4580,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
     </row>
-    <row r="129" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:10">
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4518,7 +4589,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
     </row>
-    <row r="130" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:10">
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4527,7 +4598,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
     </row>
-    <row r="131" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:10">
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4536,7 +4607,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
     </row>
-    <row r="132" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:10">
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4545,7 +4616,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
     </row>
-    <row r="133" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:10">
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4554,7 +4625,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
     </row>
-    <row r="134" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:10">
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -4563,7 +4634,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
     </row>
-    <row r="135" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:10">
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4572,7 +4643,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
     </row>
-    <row r="136" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:10">
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -4581,7 +4652,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
     </row>
-    <row r="137" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:10">
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4590,7 +4661,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
     </row>
-    <row r="138" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:10">
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -4599,7 +4670,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
     </row>
-    <row r="139" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:10">
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4608,7 +4679,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
     </row>
-    <row r="140" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:10">
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4617,7 +4688,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
     </row>
-    <row r="141" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:10">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4626,7 +4697,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
     </row>
-    <row r="142" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:10">
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -4635,7 +4706,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
     </row>
-    <row r="143" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:10">
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4644,7 +4715,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
     </row>
-    <row r="144" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:10">
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4653,7 +4724,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
     </row>
-    <row r="145" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:10">
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4662,7 +4733,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
     </row>
-    <row r="146" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:10">
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4671,7 +4742,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
     </row>
-    <row r="147" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:10">
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4680,7 +4751,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
     </row>
-    <row r="148" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:10">
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4689,7 +4760,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
     </row>
-    <row r="149" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:10">
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -4698,7 +4769,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
     </row>
-    <row r="150" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:10">
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -4707,7 +4778,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
     </row>
-    <row r="151" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:10">
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
@@ -4716,7 +4787,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
     </row>
-    <row r="152" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:10">
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4725,7 +4796,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
     </row>
-    <row r="153" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:10">
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
@@ -4734,7 +4805,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
     </row>
-    <row r="154" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:10">
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4743,7 +4814,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
     </row>
-    <row r="155" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:10">
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4752,7 +4823,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
     </row>
-    <row r="156" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:10">
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -4761,7 +4832,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
     </row>
-    <row r="157" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:10">
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
@@ -4770,7 +4841,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
     </row>
-    <row r="158" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:10">
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
@@ -4779,7 +4850,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
     </row>
-    <row r="159" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:10">
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
       <c r="F159" s="6"/>
@@ -4788,7 +4859,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
     </row>
-    <row r="160" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:10">
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
       <c r="F160" s="6"/>
@@ -4797,7 +4868,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
     </row>
-    <row r="161" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:10">
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
@@ -4806,7 +4877,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
     </row>
-    <row r="162" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:10">
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
@@ -4815,7 +4886,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
     </row>
-    <row r="163" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:10">
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
@@ -4824,7 +4895,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
     </row>
-    <row r="164" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:10">
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
@@ -4833,7 +4904,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
     </row>
-    <row r="165" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:10">
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
@@ -4842,7 +4913,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
     </row>
-    <row r="166" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:10">
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -4851,7 +4922,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
     </row>
-    <row r="167" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:10">
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
@@ -4860,7 +4931,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
     </row>
-    <row r="168" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:10">
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -4869,7 +4940,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
     </row>
-    <row r="169" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:10">
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
@@ -4878,7 +4949,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
     </row>
-    <row r="170" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:10">
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
@@ -4887,7 +4958,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:10">
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
@@ -4896,7 +4967,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:10">
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
@@ -4905,7 +4976,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
     </row>
-    <row r="173" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:10">
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
@@ -4914,7 +4985,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
     </row>
-    <row r="174" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:10">
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
@@ -4923,7 +4994,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
     </row>
-    <row r="175" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:10">
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
@@ -4932,7 +5003,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
     </row>
-    <row r="176" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:10">
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
@@ -4941,7 +5012,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
     </row>
-    <row r="177" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:10">
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
@@ -4950,7 +5021,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
     </row>
-    <row r="178" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:10">
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
@@ -4959,7 +5030,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
     </row>
-    <row r="179" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:10">
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
@@ -4968,7 +5039,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
     </row>
-    <row r="180" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:10">
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
@@ -4977,7 +5048,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
     </row>
-    <row r="181" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:10">
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
@@ -4986,7 +5057,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
     </row>
-    <row r="182" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:10">
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
@@ -4995,7 +5066,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
     </row>
-    <row r="183" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:10">
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
@@ -5004,7 +5075,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
     </row>
-    <row r="184" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:10">
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
@@ -5013,7 +5084,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
     </row>
-    <row r="185" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:10">
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
@@ -5022,7 +5093,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
     </row>
-    <row r="186" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:10">
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
@@ -5031,7 +5102,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
     </row>
-    <row r="187" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:10">
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
@@ -5040,7 +5111,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
     </row>
-    <row r="188" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:10">
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
@@ -5049,7 +5120,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
     </row>
-    <row r="189" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:10">
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
@@ -5058,7 +5129,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
     </row>
-    <row r="190" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:10">
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
@@ -5067,7 +5138,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
     </row>
-    <row r="191" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:10">
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
@@ -5076,7 +5147,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
     </row>
-    <row r="192" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:10">
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
@@ -5085,7 +5156,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
     </row>
-    <row r="193" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:10">
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
@@ -5094,7 +5165,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
     </row>
-    <row r="194" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:10">
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
@@ -5103,7 +5174,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
     </row>
-    <row r="195" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:10">
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
@@ -5112,7 +5183,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
     </row>
-    <row r="196" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:10">
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
@@ -5121,7 +5192,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
     </row>
-    <row r="197" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:10">
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
       <c r="F197" s="6"/>
@@ -5130,7 +5201,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="6"/>
     </row>
-    <row r="198" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:10">
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
       <c r="F198" s="6"/>
@@ -5139,7 +5210,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="6"/>
     </row>
-    <row r="199" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:10">
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
@@ -5148,7 +5219,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="6"/>
     </row>
-    <row r="200" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:10">
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
@@ -5157,7 +5228,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="6"/>
     </row>
-    <row r="201" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:10">
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
@@ -5166,7 +5237,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="6"/>
     </row>
-    <row r="202" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:10">
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
@@ -5175,7 +5246,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="6"/>
     </row>
-    <row r="203" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:10">
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
@@ -5184,7 +5255,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="6"/>
     </row>
-    <row r="204" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:10">
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
@@ -5193,7 +5264,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="6"/>
     </row>
-    <row r="205" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:10">
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
@@ -5202,7 +5273,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="6"/>
     </row>
-    <row r="206" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:10">
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
@@ -5211,7 +5282,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="6"/>
     </row>
-    <row r="207" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:10">
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
@@ -5220,7 +5291,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="6"/>
     </row>
-    <row r="208" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:10">
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
@@ -5229,7 +5300,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="6"/>
     </row>
-    <row r="209" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:10">
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
@@ -5238,7 +5309,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="6"/>
     </row>
-    <row r="210" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:10">
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
@@ -5247,7 +5318,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
     </row>
-    <row r="211" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:10">
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
@@ -5256,7 +5327,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="6"/>
     </row>
-    <row r="212" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:10">
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
@@ -5265,7 +5336,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
     </row>
-    <row r="213" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:10">
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
@@ -5274,7 +5345,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
     </row>
-    <row r="214" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:10">
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
@@ -5283,7 +5354,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
     </row>
-    <row r="215" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:10">
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
@@ -5292,7 +5363,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
     </row>
-    <row r="216" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:10">
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
@@ -5301,7 +5372,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
     </row>
-    <row r="217" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:10">
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
@@ -5310,7 +5381,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
     </row>
-    <row r="218" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:10">
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
@@ -5319,7 +5390,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
     </row>
-    <row r="219" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:10">
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
@@ -5328,7 +5399,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
     </row>
-    <row r="220" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:10">
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -5337,7 +5408,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="6"/>
     </row>
-    <row r="221" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:10">
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
@@ -5346,7 +5417,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="6"/>
     </row>
-    <row r="222" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:10">
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
@@ -5355,7 +5426,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="6"/>
     </row>
-    <row r="223" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:10">
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
@@ -5364,7 +5435,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="6"/>
     </row>
-    <row r="224" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:10">
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
@@ -5373,7 +5444,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="6"/>
     </row>
-    <row r="225" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:10">
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
@@ -5382,7 +5453,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="6"/>
     </row>
-    <row r="226" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:10">
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
@@ -5391,7 +5462,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="6"/>
     </row>
-    <row r="227" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:10">
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
@@ -5400,7 +5471,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="6"/>
     </row>
-    <row r="228" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:10">
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
@@ -5409,7 +5480,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="6"/>
     </row>
-    <row r="229" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:10">
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
@@ -5418,7 +5489,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="6"/>
     </row>
-    <row r="230" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:10">
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
@@ -5427,7 +5498,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="6"/>
     </row>
-    <row r="231" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:10">
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
@@ -5436,7 +5507,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="6"/>
     </row>
-    <row r="232" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:10">
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
@@ -5445,7 +5516,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="6"/>
     </row>
-    <row r="233" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:10">
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
@@ -5454,7 +5525,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="6"/>
     </row>
-    <row r="234" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:10">
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
@@ -5463,7 +5534,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="6"/>
     </row>
-    <row r="235" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:10">
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
@@ -5472,7 +5543,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="6"/>
     </row>
-    <row r="236" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:10">
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
@@ -5481,7 +5552,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="6"/>
     </row>
-    <row r="237" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:10">
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
@@ -5490,7 +5561,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="6"/>
     </row>
-    <row r="238" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:10">
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
@@ -5499,7 +5570,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="6"/>
     </row>
-    <row r="239" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:10">
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -5508,7 +5579,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="6"/>
     </row>
-    <row r="240" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:10">
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -5517,7 +5588,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="6"/>
     </row>
-    <row r="241" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:10">
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -5526,7 +5597,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="6"/>
     </row>
-    <row r="242" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:10">
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -5535,7 +5606,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="6"/>
     </row>
-    <row r="243" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:10">
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -5544,7 +5615,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="6"/>
     </row>
-    <row r="244" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:10">
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -5553,7 +5624,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="6"/>
     </row>
-    <row r="245" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:10">
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -5562,7 +5633,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="6"/>
     </row>
-    <row r="246" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:10">
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -5571,7 +5642,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="6"/>
     </row>
-    <row r="247" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:10">
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -5580,7 +5651,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="6"/>
     </row>
-    <row r="248" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:10">
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -5589,7 +5660,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
     </row>
-    <row r="249" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:10">
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -5598,7 +5669,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
     </row>
-    <row r="250" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:10">
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -5607,7 +5678,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="6"/>
     </row>
-    <row r="251" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:10">
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -5616,7 +5687,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="6"/>
     </row>
-    <row r="252" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:10">
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -5625,7 +5696,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="6"/>
     </row>
-    <row r="253" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:10">
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -5634,7 +5705,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="6"/>
     </row>
-    <row r="254" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:10">
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -5643,7 +5714,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="6"/>
     </row>
-    <row r="255" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:10">
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -5652,7 +5723,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
     </row>
-    <row r="256" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:10">
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -5661,7 +5732,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
     </row>
-    <row r="257" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:10">
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -5670,7 +5741,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
     </row>
-    <row r="258" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:10">
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -5679,7 +5750,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="6"/>
     </row>
-    <row r="259" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:10">
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -5688,7 +5759,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="6"/>
     </row>
-    <row r="260" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:10">
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -5697,7 +5768,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="6"/>
     </row>
-    <row r="261" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:10">
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -5706,7 +5777,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="6"/>
     </row>
-    <row r="262" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:10">
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -5715,7 +5786,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="6"/>
     </row>
-    <row r="263" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:10">
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
@@ -5724,7 +5795,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="6"/>
     </row>
-    <row r="264" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:10">
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
@@ -5733,7 +5804,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="6"/>
     </row>
-    <row r="265" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:10">
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
@@ -5742,7 +5813,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
     </row>
-    <row r="266" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:10">
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
@@ -5751,7 +5822,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="6"/>
     </row>
-    <row r="267" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:10">
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
@@ -5760,7 +5831,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="6"/>
     </row>
-    <row r="268" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:10">
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
@@ -5769,7 +5840,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="6"/>
     </row>
-    <row r="269" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:10">
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
@@ -5778,7 +5849,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="6"/>
     </row>
-    <row r="270" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:10">
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
@@ -5787,7 +5858,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="6"/>
     </row>
-    <row r="271" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:10">
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
@@ -5796,7 +5867,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="6"/>
     </row>
-    <row r="272" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:10">
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
@@ -5805,7 +5876,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="6"/>
     </row>
-    <row r="273" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:10">
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
@@ -5814,7 +5885,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="6"/>
     </row>
-    <row r="274" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:10">
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
@@ -5823,7 +5894,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="6"/>
     </row>
-    <row r="275" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:10">
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
@@ -5832,7 +5903,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="6"/>
     </row>
-    <row r="276" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:10">
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
@@ -5841,7 +5912,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="6"/>
     </row>
-    <row r="277" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:10">
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
@@ -5850,7 +5921,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="6"/>
     </row>
-    <row r="278" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:10">
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
@@ -5859,7 +5930,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="6"/>
     </row>
-    <row r="279" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:10">
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
@@ -5868,7 +5939,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="6"/>
     </row>
-    <row r="280" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:10">
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
@@ -5886,7 +5957,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:N53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
     <col min="3" max="3" width="10.109375" style="13" customWidth="1"/>
@@ -5898,12 +5969,12 @@
     <col min="10" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10">
       <c r="F3" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:10">
       <c r="C4" s="17" t="s">
         <v>78</v>
       </c>
@@ -5927,7 +5998,7 @@
       </c>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10">
       <c r="C5" s="14" t="s">
         <v>85</v>
       </c>
@@ -5945,7 +6016,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="15"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10">
       <c r="C6" s="14" t="s">
         <v>88</v>
       </c>
@@ -5965,12 +6036,12 @@
       <c r="I6" s="17"/>
       <c r="J6" s="15"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10">
       <c r="F10" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10">
       <c r="C11" s="17" t="s">
         <v>78</v>
       </c>
@@ -5993,7 +6064,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10">
       <c r="C12" s="14" t="s">
         <v>85</v>
       </c>
@@ -6016,7 +6087,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10">
       <c r="C13" s="14" t="s">
         <v>88</v>
       </c>
@@ -6039,12 +6110,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10">
       <c r="C16" s="18" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14">
       <c r="A17" s="20" t="s">
         <v>141</v>
       </c>
@@ -6086,7 +6157,7 @@
       </c>
       <c r="N17" s="19"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14">
       <c r="A18" s="21" t="s">
         <v>78</v>
       </c>
@@ -6130,7 +6201,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14">
       <c r="A19" s="21" t="s">
         <v>134</v>
       </c>
@@ -6172,7 +6243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14">
       <c r="A20" s="21" t="s">
         <v>153</v>
       </c>
@@ -6212,12 +6283,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14">
       <c r="C23" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14">
       <c r="B24" s="20" t="s">
         <v>143</v>
       </c>
@@ -6249,7 +6320,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14">
       <c r="B25" s="17" t="s">
         <v>126</v>
       </c>
@@ -6281,7 +6352,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14">
       <c r="B26" s="14" t="s">
         <v>91</v>
       </c>
@@ -6311,7 +6382,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14">
       <c r="B27" s="14" t="s">
         <v>154</v>
       </c>
@@ -6339,12 +6410,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27.6">
       <c r="F29" s="22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="15">
       <c r="B30" s="17" t="s">
         <v>164</v>
       </c>
@@ -6370,7 +6441,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" ht="15">
       <c r="B31" s="14">
         <v>13</v>
       </c>
@@ -6396,7 +6467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="15">
       <c r="B32" s="14">
         <v>15</v>
       </c>
@@ -6422,7 +6493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="18" t="s">
         <v>165</v>
       </c>
@@ -6451,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="18" t="s">
         <v>166</v>
       </c>
@@ -6480,7 +6551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15">
       <c r="A35" s="18" t="s">
         <v>167</v>
       </c>
@@ -6509,7 +6580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="15">
       <c r="B36" s="17">
         <v>21.4</v>
       </c>
@@ -6535,7 +6606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="15">
       <c r="B37" s="14">
         <v>35</v>
       </c>
@@ -6561,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15">
       <c r="B38" s="17">
         <v>35</v>
       </c>
@@ -6587,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" ht="15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -6610,7 +6681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="15">
       <c r="B40" s="14">
         <v>35</v>
       </c>
@@ -6633,12 +6704,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="15">
       <c r="F42" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="15">
       <c r="D43" s="16" t="s">
         <v>173</v>
       </c>
@@ -6649,7 +6720,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15">
       <c r="D44" s="16" t="s">
         <v>174</v>
       </c>
@@ -6660,7 +6731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15">
       <c r="D45" s="16" t="s">
         <v>175</v>
       </c>
@@ -6671,7 +6742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15">
       <c r="F46" s="17" t="s">
         <v>176</v>
       </c>
@@ -6679,7 +6750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="15">
       <c r="F47" s="14" t="s">
         <v>171</v>
       </c>
@@ -6687,7 +6758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="15">
       <c r="F48" s="14" t="s">
         <v>170</v>
       </c>
@@ -6695,7 +6766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="6:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="49" spans="6:7" ht="15">
       <c r="F49" s="14" t="s">
         <v>171</v>
       </c>
@@ -6703,7 +6774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="6:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="50" spans="6:7" ht="15">
       <c r="F50" s="17" t="s">
         <v>170</v>
       </c>
@@ -6711,7 +6782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="6:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="51" spans="6:7" ht="15">
       <c r="F51" s="14" t="s">
         <v>169</v>
       </c>
@@ -6719,7 +6790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="6:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="52" spans="6:7" ht="15">
       <c r="F52" s="14" t="s">
         <v>180</v>
       </c>
@@ -6727,7 +6798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="6:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="53" spans="6:7" ht="15">
       <c r="F53" s="14" t="s">
         <v>181</v>
       </c>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9B358-8679-41EB-B7BF-B6D80CC090D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E0B29A-C669-46C7-B7D9-1A507F1AE67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="356">
   <si>
     <t>Date</t>
   </si>
@@ -1407,12 +1407,31 @@
 videocapture(videopath ) -- it will detect video path 
 video capture(1) -- inf any camera outside to the system then it will detect </t>
   </si>
+  <si>
+    <t>color detection -- red , green, blue color , every colr except white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">videos - collection of frames &amp; complete video detection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocr &amp; pytessarct we are using to detect the text from image </t>
+  </si>
+  <si>
+    <t>ocr  (optical character recognition)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opecv practicles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">color detection, ocr, video - frame 
+cv2.videocapture,  red mask, green mask </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1561,7 +1580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1637,6 +1656,9 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1934,7 +1956,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F65"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="41" style="3" customWidth="1"/>
@@ -1945,7 +1967,7 @@
     <col min="7" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1981,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="90">
+    <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>45981</v>
       </c>
@@ -1970,7 +1992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="144">
+    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>45982</v>
       </c>
@@ -1981,7 +2003,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="72">
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>45985</v>
       </c>
@@ -1992,7 +2014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="72">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>45986</v>
       </c>
@@ -2003,7 +2025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="243" customHeight="1">
+    <row r="6" spans="1:6" ht="243" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>45987</v>
       </c>
@@ -2014,7 +2036,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="108">
+    <row r="7" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>45988</v>
       </c>
@@ -2025,7 +2047,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="126">
+    <row r="8" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>46019</v>
       </c>
@@ -2036,7 +2058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="202.2" customHeight="1">
+    <row r="9" spans="1:6" ht="202.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>45992</v>
       </c>
@@ -2047,7 +2069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="144">
+    <row r="10" spans="1:6" ht="144" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>45993</v>
       </c>
@@ -2058,7 +2080,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="108">
+    <row r="11" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>45994</v>
       </c>
@@ -2069,7 +2091,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="220.2" customHeight="1">
+    <row r="12" spans="1:6" ht="220.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>46000</v>
       </c>
@@ -2080,7 +2102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="126">
+    <row r="13" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>46001</v>
       </c>
@@ -2091,7 +2113,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="126">
+    <row r="14" spans="1:6" ht="126" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>46002</v>
       </c>
@@ -2102,7 +2124,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="72">
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>46003</v>
       </c>
@@ -2113,7 +2135,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="108">
+    <row r="16" spans="1:6" ht="108" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>46006</v>
       </c>
@@ -2124,7 +2146,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="126">
+    <row r="17" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>46007</v>
       </c>
@@ -2135,7 +2157,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="54">
+    <row r="18" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>46008</v>
       </c>
@@ -2146,7 +2168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="90">
+    <row r="19" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>46009</v>
       </c>
@@ -2157,7 +2179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="144">
+    <row r="20" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>46010</v>
       </c>
@@ -2168,7 +2190,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>46012</v>
       </c>
@@ -2179,7 +2201,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="144">
+    <row r="22" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>46013</v>
       </c>
@@ -2190,7 +2212,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="90">
+    <row r="23" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>46014</v>
       </c>
@@ -2201,7 +2223,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="150" customHeight="1">
+    <row r="24" spans="1:3" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>46015</v>
       </c>
@@ -2212,7 +2234,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="118.2" customHeight="1">
+    <row r="25" spans="1:3" ht="118.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>46017</v>
       </c>
@@ -2223,7 +2245,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="166.2" customHeight="1">
+    <row r="26" spans="1:3" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>46018</v>
       </c>
@@ -2234,7 +2256,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="72">
+    <row r="27" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>46020</v>
       </c>
@@ -2245,7 +2267,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="126">
+    <row r="28" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>186</v>
       </c>
@@ -2256,7 +2278,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="90.6" customHeight="1">
+    <row r="29" spans="1:3" ht="90.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>200</v>
       </c>
@@ -2267,7 +2289,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="90">
+    <row r="30" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>46027</v>
       </c>
@@ -2278,7 +2300,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="180">
+    <row r="31" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>46028</v>
       </c>
@@ -2289,7 +2311,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="126">
+    <row r="32" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>46029</v>
       </c>
@@ -2300,7 +2322,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="72">
+    <row r="33" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>46030</v>
       </c>
@@ -2311,7 +2333,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="216.6" customHeight="1">
+    <row r="34" spans="1:3" ht="216.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>46031</v>
       </c>
@@ -2322,7 +2344,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="126">
+    <row r="35" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A35" s="11">
         <v>46032</v>
       </c>
@@ -2333,7 +2355,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="168" customHeight="1">
+    <row r="36" spans="1:3" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>46034</v>
       </c>
@@ -2344,7 +2366,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="108">
+    <row r="37" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A37" s="11">
         <v>46041</v>
       </c>
@@ -2355,7 +2377,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="144">
+    <row r="38" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>46042</v>
       </c>
@@ -2366,7 +2388,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="90">
+    <row r="39" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>46043</v>
       </c>
@@ -2377,7 +2399,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="108">
+    <row r="40" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>46044</v>
       </c>
@@ -2388,7 +2410,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="108">
+    <row r="41" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A41" s="11">
         <v>46045</v>
       </c>
@@ -2399,7 +2421,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="126">
+    <row r="42" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>46046</v>
       </c>
@@ -2410,7 +2432,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="72">
+    <row r="43" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A43" s="11">
         <v>46048</v>
       </c>
@@ -2421,7 +2443,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="126">
+    <row r="44" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A44" s="11">
         <v>46049</v>
       </c>
@@ -2432,7 +2454,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="126">
+    <row r="45" spans="1:3" ht="126" x14ac:dyDescent="0.25">
       <c r="A45" s="11">
         <v>46050</v>
       </c>
@@ -2443,7 +2465,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="162">
+    <row r="46" spans="1:3" ht="162" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
         <v>46051</v>
       </c>
@@ -2454,7 +2476,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="144">
+    <row r="47" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>46052</v>
       </c>
@@ -2465,7 +2487,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="72">
+    <row r="48" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>46055</v>
       </c>
@@ -2476,7 +2498,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="144">
+    <row r="49" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>46056</v>
       </c>
@@ -2487,7 +2509,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="108">
+    <row r="50" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>46057</v>
       </c>
@@ -2498,7 +2520,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="72">
+    <row r="51" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>46058</v>
       </c>
@@ -2509,7 +2531,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="162">
+    <row r="52" spans="1:3" ht="162" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>46059</v>
       </c>
@@ -2520,7 +2542,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="72">
+    <row r="53" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A53" s="11">
         <v>46060</v>
       </c>
@@ -2531,7 +2553,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="108">
+    <row r="54" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A54" s="11">
         <v>46062</v>
       </c>
@@ -2542,7 +2564,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="54">
+    <row r="55" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>46063</v>
       </c>
@@ -2553,7 +2575,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="72">
+    <row r="56" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A56" s="11">
         <v>46064</v>
       </c>
@@ -2564,7 +2586,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="54">
+    <row r="57" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A57" s="11">
         <v>46065</v>
       </c>
@@ -2575,7 +2597,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="36">
+    <row r="58" spans="1:3" ht="36" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>46066</v>
       </c>
@@ -2586,7 +2608,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="216">
+    <row r="59" spans="1:3" ht="216" x14ac:dyDescent="0.25">
       <c r="A59" s="11">
         <v>46069</v>
       </c>
@@ -2597,7 +2619,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="90">
+    <row r="60" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>46070</v>
       </c>
@@ -2608,7 +2630,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="144">
+    <row r="61" spans="1:3" ht="144" x14ac:dyDescent="0.25">
       <c r="A61" s="11">
         <v>46071</v>
       </c>
@@ -2619,7 +2641,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="108">
+    <row r="62" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>46072</v>
       </c>
@@ -2630,7 +2652,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="72">
+    <row r="63" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A63" s="11">
         <v>46076</v>
       </c>
@@ -2641,7 +2663,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="90">
+    <row r="64" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A64" s="11">
         <v>46077</v>
       </c>
@@ -2652,11 +2674,16 @@
         <v>349</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" ht="36" x14ac:dyDescent="0.25">
       <c r="A65" s="11">
         <v>46078</v>
       </c>
-      <c r="C65" s="6"/>
+      <c r="B65" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>355</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2667,7 +2694,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K280"/>
-  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
@@ -2683,7 +2710,7 @@
     <col min="12" max="16384" width="13.77734375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
@@ -2718,7 +2745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -2738,7 +2765,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="62.4">
+    <row r="3" spans="1:11" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2758,7 +2785,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2778,7 +2805,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:11" ht="31.2">
+    <row r="5" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2798,7 +2825,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2818,7 +2845,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2838,7 +2865,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2858,7 +2885,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -2878,7 +2905,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -2898,7 +2925,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -2918,7 +2945,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="31.2">
+    <row r="12" spans="1:11" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -2938,7 +2965,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -2958,7 +2985,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:11" ht="46.8">
+    <row r="14" spans="1:11" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -2978,7 +3005,7 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -2998,7 +3025,7 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -3018,7 +3045,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -3038,7 +3065,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -3058,7 +3085,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -3078,7 +3105,7 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -3098,7 +3125,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -3118,7 +3145,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="31.2">
+    <row r="22" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -3140,7 +3167,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -3160,7 +3187,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -3180,7 +3207,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -3200,7 +3227,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -3222,7 +3249,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -3244,7 +3271,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -3266,7 +3293,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -3286,7 +3313,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -3306,7 +3333,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -3328,7 +3355,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -3348,7 +3375,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -3368,7 +3395,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -3390,7 +3417,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -3410,7 +3437,7 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>35</v>
       </c>
@@ -3430,7 +3457,7 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
     </row>
-    <row r="37" spans="1:10" ht="31.2">
+    <row r="37" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -3450,7 +3477,7 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>37</v>
       </c>
@@ -3470,7 +3497,7 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -3490,7 +3517,7 @@
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>39</v>
       </c>
@@ -3510,7 +3537,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -3530,7 +3557,7 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>41</v>
       </c>
@@ -3550,7 +3577,7 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>42</v>
       </c>
@@ -3570,7 +3597,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
     </row>
-    <row r="44" spans="1:10" ht="62.4">
+    <row r="44" spans="1:10" ht="62.4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>278</v>
       </c>
@@ -3590,7 +3617,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" ht="140.4">
+    <row r="45" spans="1:10" ht="140.4" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>281</v>
       </c>
@@ -3610,7 +3637,7 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>61</v>
       </c>
@@ -3624,7 +3651,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>62</v>
       </c>
@@ -3644,7 +3671,7 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>63</v>
       </c>
@@ -3664,7 +3691,7 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>64</v>
       </c>
@@ -3684,7 +3711,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>65</v>
       </c>
@@ -3704,7 +3731,7 @@
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>66</v>
       </c>
@@ -3724,7 +3751,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>67</v>
       </c>
@@ -3744,7 +3771,7 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>68</v>
       </c>
@@ -3764,7 +3791,7 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>69</v>
       </c>
@@ -3784,7 +3811,7 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>70</v>
       </c>
@@ -3804,7 +3831,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>71</v>
       </c>
@@ -3824,7 +3851,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>72</v>
       </c>
@@ -3844,7 +3871,7 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>73</v>
       </c>
@@ -3864,7 +3891,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>74</v>
       </c>
@@ -3884,7 +3911,7 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>75</v>
       </c>
@@ -3904,7 +3931,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>76</v>
       </c>
@@ -3924,7 +3951,7 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>77</v>
       </c>
@@ -3944,7 +3971,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>78</v>
       </c>
@@ -3964,7 +3991,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>79</v>
       </c>
@@ -3984,7 +4011,7 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="1:10" ht="46.8">
+    <row r="65" spans="1:10" ht="46.8" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
         <v>345</v>
       </c>
@@ -4004,7 +4031,7 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>86</v>
       </c>
@@ -4014,7 +4041,9 @@
       <c r="C66" s="9" t="s">
         <v>347</v>
       </c>
-      <c r="D66" s="6"/>
+      <c r="D66" s="6" t="s">
+        <v>350</v>
+      </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
@@ -4022,8 +4051,19 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="1:10">
-      <c r="D67" s="6"/>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
+        <v>87</v>
+      </c>
+      <c r="B67" s="10">
+        <v>46078</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>351</v>
+      </c>
       <c r="E67" s="6"/>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
@@ -4031,8 +4071,19 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
     </row>
-    <row r="68" spans="1:10">
-      <c r="D68" s="6"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
+        <v>88</v>
+      </c>
+      <c r="B68" s="10">
+        <v>46078</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>352</v>
+      </c>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
@@ -4040,7 +4091,13 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>89</v>
+      </c>
+      <c r="B69" s="26">
+        <v>46079</v>
+      </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
@@ -4049,7 +4106,7 @@
       <c r="I69" s="6"/>
       <c r="J69" s="6"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
@@ -4058,7 +4115,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
@@ -4067,7 +4124,7 @@
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
@@ -4076,7 +4133,7 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -4085,7 +4142,7 @@
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -4094,7 +4151,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -4103,7 +4160,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -4112,7 +4169,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -4121,7 +4178,7 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -4130,7 +4187,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -4139,7 +4196,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -4148,7 +4205,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="4:10">
+    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -4157,7 +4214,7 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" spans="4:10">
+    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -4166,7 +4223,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="4:10">
+    <row r="83" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4175,7 +4232,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" spans="4:10">
+    <row r="84" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4184,7 +4241,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="4:10">
+    <row r="85" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4193,7 +4250,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="4:10">
+    <row r="86" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -4202,7 +4259,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" spans="4:10">
+    <row r="87" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -4211,7 +4268,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
     </row>
-    <row r="88" spans="4:10">
+    <row r="88" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4220,7 +4277,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="4:10">
+    <row r="89" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4229,7 +4286,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" spans="4:10">
+    <row r="90" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4238,7 +4295,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="4:10">
+    <row r="91" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -4247,7 +4304,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" spans="4:10">
+    <row r="92" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -4256,7 +4313,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="4:10">
+    <row r="93" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4265,7 +4322,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" spans="4:10">
+    <row r="94" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4274,7 +4331,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="4:10">
+    <row r="95" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4283,7 +4340,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
     </row>
-    <row r="96" spans="4:10">
+    <row r="96" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
@@ -4292,7 +4349,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" spans="4:10">
+    <row r="97" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
@@ -4301,7 +4358,7 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
     </row>
-    <row r="98" spans="4:10">
+    <row r="98" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
@@ -4310,7 +4367,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" spans="4:10">
+    <row r="99" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
@@ -4319,7 +4376,7 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
     </row>
-    <row r="100" spans="4:10">
+    <row r="100" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
@@ -4328,7 +4385,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" spans="4:10">
+    <row r="101" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -4337,7 +4394,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
     </row>
-    <row r="102" spans="4:10">
+    <row r="102" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -4346,7 +4403,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" spans="4:10">
+    <row r="103" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -4355,7 +4412,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
     </row>
-    <row r="104" spans="4:10">
+    <row r="104" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -4364,7 +4421,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="4:10">
+    <row r="105" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -4373,7 +4430,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
     </row>
-    <row r="106" spans="4:10">
+    <row r="106" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -4382,7 +4439,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" spans="4:10">
+    <row r="107" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -4391,7 +4448,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
     </row>
-    <row r="108" spans="4:10">
+    <row r="108" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -4400,7 +4457,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="4:10">
+    <row r="109" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -4409,7 +4466,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
     </row>
-    <row r="110" spans="4:10">
+    <row r="110" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -4418,7 +4475,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" spans="4:10">
+    <row r="111" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -4427,7 +4484,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
     </row>
-    <row r="112" spans="4:10">
+    <row r="112" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -4436,7 +4493,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" spans="4:10">
+    <row r="113" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -4445,7 +4502,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
     </row>
-    <row r="114" spans="4:10">
+    <row r="114" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -4454,7 +4511,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" spans="4:10">
+    <row r="115" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -4463,7 +4520,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
     </row>
-    <row r="116" spans="4:10">
+    <row r="116" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -4472,7 +4529,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" spans="4:10">
+    <row r="117" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -4481,7 +4538,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
     </row>
-    <row r="118" spans="4:10">
+    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -4490,7 +4547,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" spans="4:10">
+    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -4499,7 +4556,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
     </row>
-    <row r="120" spans="4:10">
+    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -4508,7 +4565,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" spans="4:10">
+    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -4517,7 +4574,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
     </row>
-    <row r="122" spans="4:10">
+    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -4526,7 +4583,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" spans="4:10">
+    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -4535,7 +4592,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
     </row>
-    <row r="124" spans="4:10">
+    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -4544,7 +4601,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" spans="4:10">
+    <row r="125" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -4553,7 +4610,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" spans="4:10">
+    <row r="126" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -4562,7 +4619,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="4:10">
+    <row r="127" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -4571,7 +4628,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
     </row>
-    <row r="128" spans="4:10">
+    <row r="128" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -4580,7 +4637,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
     </row>
-    <row r="129" spans="4:10">
+    <row r="129" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -4589,7 +4646,7 @@
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
     </row>
-    <row r="130" spans="4:10">
+    <row r="130" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -4598,7 +4655,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
     </row>
-    <row r="131" spans="4:10">
+    <row r="131" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -4607,7 +4664,7 @@
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
     </row>
-    <row r="132" spans="4:10">
+    <row r="132" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -4616,7 +4673,7 @@
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
     </row>
-    <row r="133" spans="4:10">
+    <row r="133" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -4625,7 +4682,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
     </row>
-    <row r="134" spans="4:10">
+    <row r="134" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -4634,7 +4691,7 @@
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
     </row>
-    <row r="135" spans="4:10">
+    <row r="135" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -4643,7 +4700,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
     </row>
-    <row r="136" spans="4:10">
+    <row r="136" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -4652,7 +4709,7 @@
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
     </row>
-    <row r="137" spans="4:10">
+    <row r="137" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -4661,7 +4718,7 @@
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
     </row>
-    <row r="138" spans="4:10">
+    <row r="138" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -4670,7 +4727,7 @@
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
     </row>
-    <row r="139" spans="4:10">
+    <row r="139" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -4679,7 +4736,7 @@
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
     </row>
-    <row r="140" spans="4:10">
+    <row r="140" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -4688,7 +4745,7 @@
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
     </row>
-    <row r="141" spans="4:10">
+    <row r="141" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -4697,7 +4754,7 @@
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
     </row>
-    <row r="142" spans="4:10">
+    <row r="142" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
@@ -4706,7 +4763,7 @@
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
     </row>
-    <row r="143" spans="4:10">
+    <row r="143" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
       <c r="F143" s="6"/>
@@ -4715,7 +4772,7 @@
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
     </row>
-    <row r="144" spans="4:10">
+    <row r="144" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -4724,7 +4781,7 @@
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
     </row>
-    <row r="145" spans="4:10">
+    <row r="145" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
       <c r="F145" s="6"/>
@@ -4733,7 +4790,7 @@
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
     </row>
-    <row r="146" spans="4:10">
+    <row r="146" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
       <c r="F146" s="6"/>
@@ -4742,7 +4799,7 @@
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
     </row>
-    <row r="147" spans="4:10">
+    <row r="147" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
       <c r="F147" s="6"/>
@@ -4751,7 +4808,7 @@
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
     </row>
-    <row r="148" spans="4:10">
+    <row r="148" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -4760,7 +4817,7 @@
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
     </row>
-    <row r="149" spans="4:10">
+    <row r="149" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -4769,7 +4826,7 @@
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
     </row>
-    <row r="150" spans="4:10">
+    <row r="150" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
       <c r="F150" s="6"/>
@@ -4778,7 +4835,7 @@
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
     </row>
-    <row r="151" spans="4:10">
+    <row r="151" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
       <c r="F151" s="6"/>
@@ -4787,7 +4844,7 @@
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
     </row>
-    <row r="152" spans="4:10">
+    <row r="152" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
@@ -4796,7 +4853,7 @@
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
     </row>
-    <row r="153" spans="4:10">
+    <row r="153" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
       <c r="F153" s="6"/>
@@ -4805,7 +4862,7 @@
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
     </row>
-    <row r="154" spans="4:10">
+    <row r="154" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
       <c r="F154" s="6"/>
@@ -4814,7 +4871,7 @@
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
     </row>
-    <row r="155" spans="4:10">
+    <row r="155" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
       <c r="F155" s="6"/>
@@ -4823,7 +4880,7 @@
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
     </row>
-    <row r="156" spans="4:10">
+    <row r="156" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -4832,7 +4889,7 @@
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
     </row>
-    <row r="157" spans="4:10">
+    <row r="157" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
       <c r="F157" s="6"/>
@@ -4841,7 +4898,7 @@
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
     </row>
-    <row r="158" spans="4:10">
+    <row r="158" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
       <c r="F158" s="6"/>
@@ -4850,7 +4907,7 @@
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
     </row>
-    <row r="159" spans="4:10">
+    <row r="159" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
       <c r="F159" s="6"/>
@@ -4859,7 +4916,7 @@
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
     </row>
-    <row r="160" spans="4:10">
+    <row r="160" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
       <c r="F160" s="6"/>
@@ -4868,7 +4925,7 @@
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
     </row>
-    <row r="161" spans="4:10">
+    <row r="161" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
       <c r="F161" s="6"/>
@@ -4877,7 +4934,7 @@
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
     </row>
-    <row r="162" spans="4:10">
+    <row r="162" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
@@ -4886,7 +4943,7 @@
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
     </row>
-    <row r="163" spans="4:10">
+    <row r="163" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
@@ -4895,7 +4952,7 @@
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
     </row>
-    <row r="164" spans="4:10">
+    <row r="164" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
       <c r="F164" s="6"/>
@@ -4904,7 +4961,7 @@
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
     </row>
-    <row r="165" spans="4:10">
+    <row r="165" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
       <c r="F165" s="6"/>
@@ -4913,7 +4970,7 @@
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
     </row>
-    <row r="166" spans="4:10">
+    <row r="166" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
@@ -4922,7 +4979,7 @@
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
     </row>
-    <row r="167" spans="4:10">
+    <row r="167" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
       <c r="F167" s="6"/>
@@ -4931,7 +4988,7 @@
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
     </row>
-    <row r="168" spans="4:10">
+    <row r="168" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -4940,7 +4997,7 @@
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
     </row>
-    <row r="169" spans="4:10">
+    <row r="169" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
       <c r="F169" s="6"/>
@@ -4949,7 +5006,7 @@
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
     </row>
-    <row r="170" spans="4:10">
+    <row r="170" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
       <c r="F170" s="6"/>
@@ -4958,7 +5015,7 @@
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
     </row>
-    <row r="171" spans="4:10">
+    <row r="171" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
       <c r="F171" s="6"/>
@@ -4967,7 +5024,7 @@
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
     </row>
-    <row r="172" spans="4:10">
+    <row r="172" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
       <c r="F172" s="6"/>
@@ -4976,7 +5033,7 @@
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
     </row>
-    <row r="173" spans="4:10">
+    <row r="173" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
@@ -4985,7 +5042,7 @@
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
     </row>
-    <row r="174" spans="4:10">
+    <row r="174" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
       <c r="F174" s="6"/>
@@ -4994,7 +5051,7 @@
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
     </row>
-    <row r="175" spans="4:10">
+    <row r="175" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
       <c r="F175" s="6"/>
@@ -5003,7 +5060,7 @@
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
     </row>
-    <row r="176" spans="4:10">
+    <row r="176" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
@@ -5012,7 +5069,7 @@
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
     </row>
-    <row r="177" spans="4:10">
+    <row r="177" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
       <c r="F177" s="6"/>
@@ -5021,7 +5078,7 @@
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
     </row>
-    <row r="178" spans="4:10">
+    <row r="178" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
       <c r="F178" s="6"/>
@@ -5030,7 +5087,7 @@
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
     </row>
-    <row r="179" spans="4:10">
+    <row r="179" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
       <c r="F179" s="6"/>
@@ -5039,7 +5096,7 @@
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
     </row>
-    <row r="180" spans="4:10">
+    <row r="180" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
       <c r="F180" s="6"/>
@@ -5048,7 +5105,7 @@
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
     </row>
-    <row r="181" spans="4:10">
+    <row r="181" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
       <c r="F181" s="6"/>
@@ -5057,7 +5114,7 @@
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
     </row>
-    <row r="182" spans="4:10">
+    <row r="182" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
       <c r="F182" s="6"/>
@@ -5066,7 +5123,7 @@
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
     </row>
-    <row r="183" spans="4:10">
+    <row r="183" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
       <c r="F183" s="6"/>
@@ -5075,7 +5132,7 @@
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
     </row>
-    <row r="184" spans="4:10">
+    <row r="184" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
       <c r="F184" s="6"/>
@@ -5084,7 +5141,7 @@
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
     </row>
-    <row r="185" spans="4:10">
+    <row r="185" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
@@ -5093,7 +5150,7 @@
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
     </row>
-    <row r="186" spans="4:10">
+    <row r="186" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
@@ -5102,7 +5159,7 @@
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
     </row>
-    <row r="187" spans="4:10">
+    <row r="187" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
@@ -5111,7 +5168,7 @@
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
     </row>
-    <row r="188" spans="4:10">
+    <row r="188" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
@@ -5120,7 +5177,7 @@
       <c r="I188" s="6"/>
       <c r="J188" s="6"/>
     </row>
-    <row r="189" spans="4:10">
+    <row r="189" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
@@ -5129,7 +5186,7 @@
       <c r="I189" s="6"/>
       <c r="J189" s="6"/>
     </row>
-    <row r="190" spans="4:10">
+    <row r="190" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
@@ -5138,7 +5195,7 @@
       <c r="I190" s="6"/>
       <c r="J190" s="6"/>
     </row>
-    <row r="191" spans="4:10">
+    <row r="191" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
       <c r="F191" s="6"/>
@@ -5147,7 +5204,7 @@
       <c r="I191" s="6"/>
       <c r="J191" s="6"/>
     </row>
-    <row r="192" spans="4:10">
+    <row r="192" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
       <c r="F192" s="6"/>
@@ -5156,7 +5213,7 @@
       <c r="I192" s="6"/>
       <c r="J192" s="6"/>
     </row>
-    <row r="193" spans="4:10">
+    <row r="193" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
@@ -5165,7 +5222,7 @@
       <c r="I193" s="6"/>
       <c r="J193" s="6"/>
     </row>
-    <row r="194" spans="4:10">
+    <row r="194" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
@@ -5174,7 +5231,7 @@
       <c r="I194" s="6"/>
       <c r="J194" s="6"/>
     </row>
-    <row r="195" spans="4:10">
+    <row r="195" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
       <c r="F195" s="6"/>
@@ -5183,7 +5240,7 @@
       <c r="I195" s="6"/>
       <c r="J195" s="6"/>
     </row>
-    <row r="196" spans="4:10">
+    <row r="196" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
@@ -5192,7 +5249,7 @@
       <c r="I196" s="6"/>
       <c r="J196" s="6"/>
     </row>
-    <row r="197" spans="4:10">
+    <row r="197" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
       <c r="F197" s="6"/>
@@ -5201,7 +5258,7 @@
       <c r="I197" s="6"/>
       <c r="J197" s="6"/>
     </row>
-    <row r="198" spans="4:10">
+    <row r="198" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
       <c r="F198" s="6"/>
@@ -5210,7 +5267,7 @@
       <c r="I198" s="6"/>
       <c r="J198" s="6"/>
     </row>
-    <row r="199" spans="4:10">
+    <row r="199" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
       <c r="F199" s="6"/>
@@ -5219,7 +5276,7 @@
       <c r="I199" s="6"/>
       <c r="J199" s="6"/>
     </row>
-    <row r="200" spans="4:10">
+    <row r="200" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
       <c r="F200" s="6"/>
@@ -5228,7 +5285,7 @@
       <c r="I200" s="6"/>
       <c r="J200" s="6"/>
     </row>
-    <row r="201" spans="4:10">
+    <row r="201" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
       <c r="F201" s="6"/>
@@ -5237,7 +5294,7 @@
       <c r="I201" s="6"/>
       <c r="J201" s="6"/>
     </row>
-    <row r="202" spans="4:10">
+    <row r="202" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="6"/>
       <c r="F202" s="6"/>
@@ -5246,7 +5303,7 @@
       <c r="I202" s="6"/>
       <c r="J202" s="6"/>
     </row>
-    <row r="203" spans="4:10">
+    <row r="203" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
@@ -5255,7 +5312,7 @@
       <c r="I203" s="6"/>
       <c r="J203" s="6"/>
     </row>
-    <row r="204" spans="4:10">
+    <row r="204" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
       <c r="F204" s="6"/>
@@ -5264,7 +5321,7 @@
       <c r="I204" s="6"/>
       <c r="J204" s="6"/>
     </row>
-    <row r="205" spans="4:10">
+    <row r="205" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
       <c r="F205" s="6"/>
@@ -5273,7 +5330,7 @@
       <c r="I205" s="6"/>
       <c r="J205" s="6"/>
     </row>
-    <row r="206" spans="4:10">
+    <row r="206" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
@@ -5282,7 +5339,7 @@
       <c r="I206" s="6"/>
       <c r="J206" s="6"/>
     </row>
-    <row r="207" spans="4:10">
+    <row r="207" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
@@ -5291,7 +5348,7 @@
       <c r="I207" s="6"/>
       <c r="J207" s="6"/>
     </row>
-    <row r="208" spans="4:10">
+    <row r="208" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
@@ -5300,7 +5357,7 @@
       <c r="I208" s="6"/>
       <c r="J208" s="6"/>
     </row>
-    <row r="209" spans="4:10">
+    <row r="209" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
@@ -5309,7 +5366,7 @@
       <c r="I209" s="6"/>
       <c r="J209" s="6"/>
     </row>
-    <row r="210" spans="4:10">
+    <row r="210" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
@@ -5318,7 +5375,7 @@
       <c r="I210" s="6"/>
       <c r="J210" s="6"/>
     </row>
-    <row r="211" spans="4:10">
+    <row r="211" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="6"/>
       <c r="F211" s="6"/>
@@ -5327,7 +5384,7 @@
       <c r="I211" s="6"/>
       <c r="J211" s="6"/>
     </row>
-    <row r="212" spans="4:10">
+    <row r="212" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="6"/>
       <c r="F212" s="6"/>
@@ -5336,7 +5393,7 @@
       <c r="I212" s="6"/>
       <c r="J212" s="6"/>
     </row>
-    <row r="213" spans="4:10">
+    <row r="213" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="6"/>
       <c r="F213" s="6"/>
@@ -5345,7 +5402,7 @@
       <c r="I213" s="6"/>
       <c r="J213" s="6"/>
     </row>
-    <row r="214" spans="4:10">
+    <row r="214" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="6"/>
       <c r="F214" s="6"/>
@@ -5354,7 +5411,7 @@
       <c r="I214" s="6"/>
       <c r="J214" s="6"/>
     </row>
-    <row r="215" spans="4:10">
+    <row r="215" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="6"/>
       <c r="F215" s="6"/>
@@ -5363,7 +5420,7 @@
       <c r="I215" s="6"/>
       <c r="J215" s="6"/>
     </row>
-    <row r="216" spans="4:10">
+    <row r="216" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
       <c r="F216" s="6"/>
@@ -5372,7 +5429,7 @@
       <c r="I216" s="6"/>
       <c r="J216" s="6"/>
     </row>
-    <row r="217" spans="4:10">
+    <row r="217" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="6"/>
       <c r="F217" s="6"/>
@@ -5381,7 +5438,7 @@
       <c r="I217" s="6"/>
       <c r="J217" s="6"/>
     </row>
-    <row r="218" spans="4:10">
+    <row r="218" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="6"/>
       <c r="F218" s="6"/>
@@ -5390,7 +5447,7 @@
       <c r="I218" s="6"/>
       <c r="J218" s="6"/>
     </row>
-    <row r="219" spans="4:10">
+    <row r="219" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="6"/>
       <c r="F219" s="6"/>
@@ -5399,7 +5456,7 @@
       <c r="I219" s="6"/>
       <c r="J219" s="6"/>
     </row>
-    <row r="220" spans="4:10">
+    <row r="220" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="6"/>
       <c r="F220" s="6"/>
@@ -5408,7 +5465,7 @@
       <c r="I220" s="6"/>
       <c r="J220" s="6"/>
     </row>
-    <row r="221" spans="4:10">
+    <row r="221" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="6"/>
       <c r="F221" s="6"/>
@@ -5417,7 +5474,7 @@
       <c r="I221" s="6"/>
       <c r="J221" s="6"/>
     </row>
-    <row r="222" spans="4:10">
+    <row r="222" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
       <c r="F222" s="6"/>
@@ -5426,7 +5483,7 @@
       <c r="I222" s="6"/>
       <c r="J222" s="6"/>
     </row>
-    <row r="223" spans="4:10">
+    <row r="223" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="6"/>
       <c r="F223" s="6"/>
@@ -5435,7 +5492,7 @@
       <c r="I223" s="6"/>
       <c r="J223" s="6"/>
     </row>
-    <row r="224" spans="4:10">
+    <row r="224" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="6"/>
       <c r="F224" s="6"/>
@@ -5444,7 +5501,7 @@
       <c r="I224" s="6"/>
       <c r="J224" s="6"/>
     </row>
-    <row r="225" spans="4:10">
+    <row r="225" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="6"/>
       <c r="F225" s="6"/>
@@ -5453,7 +5510,7 @@
       <c r="I225" s="6"/>
       <c r="J225" s="6"/>
     </row>
-    <row r="226" spans="4:10">
+    <row r="226" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="6"/>
       <c r="F226" s="6"/>
@@ -5462,7 +5519,7 @@
       <c r="I226" s="6"/>
       <c r="J226" s="6"/>
     </row>
-    <row r="227" spans="4:10">
+    <row r="227" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="6"/>
       <c r="F227" s="6"/>
@@ -5471,7 +5528,7 @@
       <c r="I227" s="6"/>
       <c r="J227" s="6"/>
     </row>
-    <row r="228" spans="4:10">
+    <row r="228" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="6"/>
       <c r="F228" s="6"/>
@@ -5480,7 +5537,7 @@
       <c r="I228" s="6"/>
       <c r="J228" s="6"/>
     </row>
-    <row r="229" spans="4:10">
+    <row r="229" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="6"/>
       <c r="F229" s="6"/>
@@ -5489,7 +5546,7 @@
       <c r="I229" s="6"/>
       <c r="J229" s="6"/>
     </row>
-    <row r="230" spans="4:10">
+    <row r="230" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="6"/>
       <c r="F230" s="6"/>
@@ -5498,7 +5555,7 @@
       <c r="I230" s="6"/>
       <c r="J230" s="6"/>
     </row>
-    <row r="231" spans="4:10">
+    <row r="231" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="6"/>
       <c r="F231" s="6"/>
@@ -5507,7 +5564,7 @@
       <c r="I231" s="6"/>
       <c r="J231" s="6"/>
     </row>
-    <row r="232" spans="4:10">
+    <row r="232" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="6"/>
       <c r="F232" s="6"/>
@@ -5516,7 +5573,7 @@
       <c r="I232" s="6"/>
       <c r="J232" s="6"/>
     </row>
-    <row r="233" spans="4:10">
+    <row r="233" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="6"/>
       <c r="F233" s="6"/>
@@ -5525,7 +5582,7 @@
       <c r="I233" s="6"/>
       <c r="J233" s="6"/>
     </row>
-    <row r="234" spans="4:10">
+    <row r="234" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="6"/>
       <c r="F234" s="6"/>
@@ -5534,7 +5591,7 @@
       <c r="I234" s="6"/>
       <c r="J234" s="6"/>
     </row>
-    <row r="235" spans="4:10">
+    <row r="235" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="6"/>
       <c r="F235" s="6"/>
@@ -5543,7 +5600,7 @@
       <c r="I235" s="6"/>
       <c r="J235" s="6"/>
     </row>
-    <row r="236" spans="4:10">
+    <row r="236" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="6"/>
       <c r="F236" s="6"/>
@@ -5552,7 +5609,7 @@
       <c r="I236" s="6"/>
       <c r="J236" s="6"/>
     </row>
-    <row r="237" spans="4:10">
+    <row r="237" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="6"/>
       <c r="F237" s="6"/>
@@ -5561,7 +5618,7 @@
       <c r="I237" s="6"/>
       <c r="J237" s="6"/>
     </row>
-    <row r="238" spans="4:10">
+    <row r="238" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="6"/>
       <c r="F238" s="6"/>
@@ -5570,7 +5627,7 @@
       <c r="I238" s="6"/>
       <c r="J238" s="6"/>
     </row>
-    <row r="239" spans="4:10">
+    <row r="239" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="6"/>
       <c r="F239" s="6"/>
@@ -5579,7 +5636,7 @@
       <c r="I239" s="6"/>
       <c r="J239" s="6"/>
     </row>
-    <row r="240" spans="4:10">
+    <row r="240" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="6"/>
       <c r="F240" s="6"/>
@@ -5588,7 +5645,7 @@
       <c r="I240" s="6"/>
       <c r="J240" s="6"/>
     </row>
-    <row r="241" spans="4:10">
+    <row r="241" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="6"/>
@@ -5597,7 +5654,7 @@
       <c r="I241" s="6"/>
       <c r="J241" s="6"/>
     </row>
-    <row r="242" spans="4:10">
+    <row r="242" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="6"/>
       <c r="F242" s="6"/>
@@ -5606,7 +5663,7 @@
       <c r="I242" s="6"/>
       <c r="J242" s="6"/>
     </row>
-    <row r="243" spans="4:10">
+    <row r="243" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="6"/>
       <c r="F243" s="6"/>
@@ -5615,7 +5672,7 @@
       <c r="I243" s="6"/>
       <c r="J243" s="6"/>
     </row>
-    <row r="244" spans="4:10">
+    <row r="244" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="6"/>
       <c r="F244" s="6"/>
@@ -5624,7 +5681,7 @@
       <c r="I244" s="6"/>
       <c r="J244" s="6"/>
     </row>
-    <row r="245" spans="4:10">
+    <row r="245" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="6"/>
       <c r="F245" s="6"/>
@@ -5633,7 +5690,7 @@
       <c r="I245" s="6"/>
       <c r="J245" s="6"/>
     </row>
-    <row r="246" spans="4:10">
+    <row r="246" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="6"/>
       <c r="F246" s="6"/>
@@ -5642,7 +5699,7 @@
       <c r="I246" s="6"/>
       <c r="J246" s="6"/>
     </row>
-    <row r="247" spans="4:10">
+    <row r="247" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="6"/>
@@ -5651,7 +5708,7 @@
       <c r="I247" s="6"/>
       <c r="J247" s="6"/>
     </row>
-    <row r="248" spans="4:10">
+    <row r="248" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="6"/>
@@ -5660,7 +5717,7 @@
       <c r="I248" s="6"/>
       <c r="J248" s="6"/>
     </row>
-    <row r="249" spans="4:10">
+    <row r="249" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="6"/>
@@ -5669,7 +5726,7 @@
       <c r="I249" s="6"/>
       <c r="J249" s="6"/>
     </row>
-    <row r="250" spans="4:10">
+    <row r="250" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="6"/>
       <c r="F250" s="6"/>
@@ -5678,7 +5735,7 @@
       <c r="I250" s="6"/>
       <c r="J250" s="6"/>
     </row>
-    <row r="251" spans="4:10">
+    <row r="251" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="6"/>
       <c r="F251" s="6"/>
@@ -5687,7 +5744,7 @@
       <c r="I251" s="6"/>
       <c r="J251" s="6"/>
     </row>
-    <row r="252" spans="4:10">
+    <row r="252" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="6"/>
       <c r="F252" s="6"/>
@@ -5696,7 +5753,7 @@
       <c r="I252" s="6"/>
       <c r="J252" s="6"/>
     </row>
-    <row r="253" spans="4:10">
+    <row r="253" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="6"/>
       <c r="F253" s="6"/>
@@ -5705,7 +5762,7 @@
       <c r="I253" s="6"/>
       <c r="J253" s="6"/>
     </row>
-    <row r="254" spans="4:10">
+    <row r="254" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="6"/>
       <c r="F254" s="6"/>
@@ -5714,7 +5771,7 @@
       <c r="I254" s="6"/>
       <c r="J254" s="6"/>
     </row>
-    <row r="255" spans="4:10">
+    <row r="255" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="6"/>
       <c r="F255" s="6"/>
@@ -5723,7 +5780,7 @@
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
     </row>
-    <row r="256" spans="4:10">
+    <row r="256" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="6"/>
       <c r="F256" s="6"/>
@@ -5732,7 +5789,7 @@
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
     </row>
-    <row r="257" spans="4:10">
+    <row r="257" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="6"/>
       <c r="F257" s="6"/>
@@ -5741,7 +5798,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
     </row>
-    <row r="258" spans="4:10">
+    <row r="258" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="6"/>
       <c r="F258" s="6"/>
@@ -5750,7 +5807,7 @@
       <c r="I258" s="6"/>
       <c r="J258" s="6"/>
     </row>
-    <row r="259" spans="4:10">
+    <row r="259" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="6"/>
       <c r="F259" s="6"/>
@@ -5759,7 +5816,7 @@
       <c r="I259" s="6"/>
       <c r="J259" s="6"/>
     </row>
-    <row r="260" spans="4:10">
+    <row r="260" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="6"/>
       <c r="F260" s="6"/>
@@ -5768,7 +5825,7 @@
       <c r="I260" s="6"/>
       <c r="J260" s="6"/>
     </row>
-    <row r="261" spans="4:10">
+    <row r="261" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="6"/>
       <c r="F261" s="6"/>
@@ -5777,7 +5834,7 @@
       <c r="I261" s="6"/>
       <c r="J261" s="6"/>
     </row>
-    <row r="262" spans="4:10">
+    <row r="262" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="6"/>
       <c r="F262" s="6"/>
@@ -5786,7 +5843,7 @@
       <c r="I262" s="6"/>
       <c r="J262" s="6"/>
     </row>
-    <row r="263" spans="4:10">
+    <row r="263" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="6"/>
       <c r="F263" s="6"/>
@@ -5795,7 +5852,7 @@
       <c r="I263" s="6"/>
       <c r="J263" s="6"/>
     </row>
-    <row r="264" spans="4:10">
+    <row r="264" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="6"/>
       <c r="F264" s="6"/>
@@ -5804,7 +5861,7 @@
       <c r="I264" s="6"/>
       <c r="J264" s="6"/>
     </row>
-    <row r="265" spans="4:10">
+    <row r="265" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="6"/>
       <c r="F265" s="6"/>
@@ -5813,7 +5870,7 @@
       <c r="I265" s="6"/>
       <c r="J265" s="6"/>
     </row>
-    <row r="266" spans="4:10">
+    <row r="266" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="6"/>
       <c r="F266" s="6"/>
@@ -5822,7 +5879,7 @@
       <c r="I266" s="6"/>
       <c r="J266" s="6"/>
     </row>
-    <row r="267" spans="4:10">
+    <row r="267" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="6"/>
       <c r="F267" s="6"/>
@@ -5831,7 +5888,7 @@
       <c r="I267" s="6"/>
       <c r="J267" s="6"/>
     </row>
-    <row r="268" spans="4:10">
+    <row r="268" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="6"/>
       <c r="F268" s="6"/>
@@ -5840,7 +5897,7 @@
       <c r="I268" s="6"/>
       <c r="J268" s="6"/>
     </row>
-    <row r="269" spans="4:10">
+    <row r="269" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="6"/>
       <c r="F269" s="6"/>
@@ -5849,7 +5906,7 @@
       <c r="I269" s="6"/>
       <c r="J269" s="6"/>
     </row>
-    <row r="270" spans="4:10">
+    <row r="270" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="6"/>
       <c r="F270" s="6"/>
@@ -5858,7 +5915,7 @@
       <c r="I270" s="6"/>
       <c r="J270" s="6"/>
     </row>
-    <row r="271" spans="4:10">
+    <row r="271" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="6"/>
       <c r="F271" s="6"/>
@@ -5867,7 +5924,7 @@
       <c r="I271" s="6"/>
       <c r="J271" s="6"/>
     </row>
-    <row r="272" spans="4:10">
+    <row r="272" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="6"/>
       <c r="F272" s="6"/>
@@ -5876,7 +5933,7 @@
       <c r="I272" s="6"/>
       <c r="J272" s="6"/>
     </row>
-    <row r="273" spans="4:10">
+    <row r="273" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="6"/>
       <c r="F273" s="6"/>
@@ -5885,7 +5942,7 @@
       <c r="I273" s="6"/>
       <c r="J273" s="6"/>
     </row>
-    <row r="274" spans="4:10">
+    <row r="274" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="6"/>
       <c r="F274" s="6"/>
@@ -5894,7 +5951,7 @@
       <c r="I274" s="6"/>
       <c r="J274" s="6"/>
     </row>
-    <row r="275" spans="4:10">
+    <row r="275" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="6"/>
       <c r="F275" s="6"/>
@@ -5903,7 +5960,7 @@
       <c r="I275" s="6"/>
       <c r="J275" s="6"/>
     </row>
-    <row r="276" spans="4:10">
+    <row r="276" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="6"/>
       <c r="F276" s="6"/>
@@ -5912,7 +5969,7 @@
       <c r="I276" s="6"/>
       <c r="J276" s="6"/>
     </row>
-    <row r="277" spans="4:10">
+    <row r="277" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="6"/>
       <c r="F277" s="6"/>
@@ -5921,7 +5978,7 @@
       <c r="I277" s="6"/>
       <c r="J277" s="6"/>
     </row>
-    <row r="278" spans="4:10">
+    <row r="278" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="6"/>
       <c r="F278" s="6"/>
@@ -5930,7 +5987,7 @@
       <c r="I278" s="6"/>
       <c r="J278" s="6"/>
     </row>
-    <row r="279" spans="4:10">
+    <row r="279" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="6"/>
       <c r="F279" s="6"/>
@@ -5939,7 +5996,7 @@
       <c r="I279" s="6"/>
       <c r="J279" s="6"/>
     </row>
-    <row r="280" spans="4:10">
+    <row r="280" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="6"/>
       <c r="F280" s="6"/>
@@ -5957,7 +6014,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:N53"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="13"/>
     <col min="3" max="3" width="10.109375" style="13" customWidth="1"/>
@@ -5969,12 +6026,12 @@
     <col min="10" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10">
+    <row r="3" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F3" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="3:10">
+    <row r="4" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C4" s="17" t="s">
         <v>78</v>
       </c>
@@ -5998,7 +6055,7 @@
       </c>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C5" s="14" t="s">
         <v>85</v>
       </c>
@@ -6016,7 +6073,7 @@
       <c r="I5" s="17"/>
       <c r="J5" s="15"/>
     </row>
-    <row r="6" spans="3:10">
+    <row r="6" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
         <v>88</v>
       </c>
@@ -6036,12 +6093,12 @@
       <c r="I6" s="17"/>
       <c r="J6" s="15"/>
     </row>
-    <row r="10" spans="3:10">
+    <row r="10" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F10" s="16" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="3:10">
+    <row r="11" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C11" s="17" t="s">
         <v>78</v>
       </c>
@@ -6064,7 +6121,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="3:10">
+    <row r="12" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C12" s="14" t="s">
         <v>85</v>
       </c>
@@ -6087,7 +6144,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="3:10">
+    <row r="13" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C13" s="14" t="s">
         <v>88</v>
       </c>
@@ -6110,12 +6167,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="3:10">
+    <row r="16" spans="3:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C16" s="18" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>141</v>
       </c>
@@ -6157,7 +6214,7 @@
       </c>
       <c r="N17" s="19"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>78</v>
       </c>
@@ -6201,7 +6258,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>134</v>
       </c>
@@ -6243,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>153</v>
       </c>
@@ -6283,12 +6340,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="C23" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B24" s="20" t="s">
         <v>143</v>
       </c>
@@ -6320,7 +6377,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B25" s="17" t="s">
         <v>126</v>
       </c>
@@ -6352,7 +6409,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
         <v>91</v>
       </c>
@@ -6382,7 +6439,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B27" s="14" t="s">
         <v>154</v>
       </c>
@@ -6410,12 +6467,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27.6">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F29" s="22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15">
+    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B30" s="17" t="s">
         <v>164</v>
       </c>
@@ -6441,7 +6498,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15">
+    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B31" s="14">
         <v>13</v>
       </c>
@@ -6467,7 +6524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15">
+    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>15</v>
       </c>
@@ -6493,7 +6550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15">
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>165</v>
       </c>
@@ -6522,7 +6579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15">
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>166</v>
       </c>
@@ -6551,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15">
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>167</v>
       </c>
@@ -6580,7 +6637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15">
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B36" s="17">
         <v>21.4</v>
       </c>
@@ -6606,7 +6663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15">
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B37" s="14">
         <v>35</v>
       </c>
@@ -6632,7 +6689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15">
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B38" s="17">
         <v>35</v>
       </c>
@@ -6658,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15">
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -6681,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15">
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="B40" s="14">
         <v>35</v>
       </c>
@@ -6704,12 +6761,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15">
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F42" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15">
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D43" s="16" t="s">
         <v>173</v>
       </c>
@@ -6720,7 +6777,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15">
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D44" s="16" t="s">
         <v>174</v>
       </c>
@@ -6731,7 +6788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15">
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="D45" s="16" t="s">
         <v>175</v>
       </c>
@@ -6742,7 +6799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15">
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F46" s="17" t="s">
         <v>176</v>
       </c>
@@ -6750,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15">
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F47" s="14" t="s">
         <v>171</v>
       </c>
@@ -6758,7 +6815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15">
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="F48" s="14" t="s">
         <v>170</v>
       </c>
@@ -6766,7 +6823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="6:7" ht="15">
+    <row r="49" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F49" s="14" t="s">
         <v>171</v>
       </c>
@@ -6774,7 +6831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="6:7" ht="15">
+    <row r="50" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F50" s="17" t="s">
         <v>170</v>
       </c>
@@ -6782,7 +6839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="6:7" ht="15">
+    <row r="51" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F51" s="14" t="s">
         <v>169</v>
       </c>
@@ -6790,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="6:7" ht="15">
+    <row r="52" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F52" s="14" t="s">
         <v>180</v>
       </c>
@@ -6798,7 +6855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="6:7" ht="15">
+    <row r="53" spans="6:7" ht="15" x14ac:dyDescent="0.3">
       <c r="F53" s="14" t="s">
         <v>181</v>
       </c>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E0B29A-C669-46C7-B7D9-1A507F1AE67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D96ED3-A610-416F-BBB5-486378B37A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'18th July - Agenda Sheet'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="374">
   <si>
     <t>Date</t>
   </si>
@@ -1425,6 +1430,67 @@
   <si>
     <t xml:space="preserve">color detection, ocr, video - frame 
 cv2.videocapture,  red mask, green mask </t>
+  </si>
+  <si>
+    <t xml:space="preserve">opencv </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ultralytics yolo </t>
+  </si>
+  <si>
+    <t>Multiclass classifiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fruit class classification &amp; fashon mnist </t>
+  </si>
+  <si>
+    <t>Advance computer vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">virtual hand gesture and write anything </t>
+  </si>
+  <si>
+    <t>multiclass classification !wget | bitbucket 
+tensorflowlite model | fashion mnist | virtual hand gesture | dropout -- 0.5 | 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultralytics (yolo) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">object detection using cpu &amp; gpu
+video detection, git hub repo -- </t>
+  </si>
+  <si>
+    <t>yolo model we worked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RNN(Recurant Neural Network) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">bert chatbot using pretrained model </t>
+  </si>
+  <si>
+    <t>RNN project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next word prediction model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">speech recognition  | whatsapp messaging using pywhatkit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro to gen ai | why it is popular | how to build gen ai model ?
+Gans -- generaative advaersial neural network 
+generator &amp; discriimination  | discriminator -- try to predict real or fake | 
+generate random image till image is real | both architecure run simultaneously 
+how to get data to build gen ai model 
+clip -- taming transformer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative ai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen ai model without using api using api </t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1656,9 +1722,6 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1955,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2683,6 +2746,39 @@
       </c>
       <c r="C65" s="2" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="A66" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+      <c r="A68" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4092,13 +4188,18 @@
       <c r="J68" s="6"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
+      <c r="A69" s="9">
         <v>89</v>
       </c>
-      <c r="B69" s="26">
+      <c r="B69" s="10">
         <v>46079</v>
       </c>
-      <c r="D69" s="6"/>
+      <c r="C69" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
@@ -4107,7 +4208,18 @@
       <c r="J69" s="6"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D70" s="6"/>
+      <c r="A70" s="9">
+        <v>90</v>
+      </c>
+      <c r="B70" s="10">
+        <v>46079</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>361</v>
+      </c>
       <c r="E70" s="6"/>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
@@ -4115,8 +4227,19 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D71" s="6"/>
+    <row r="71" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
+        <v>91</v>
+      </c>
+      <c r="B71" s="10">
+        <v>46079</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -4125,7 +4248,18 @@
       <c r="J71" s="6"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D72" s="6"/>
+      <c r="A72" s="9">
+        <v>92</v>
+      </c>
+      <c r="B72" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>367</v>
+      </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
@@ -4134,7 +4268,18 @@
       <c r="J72" s="6"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D73" s="6"/>
+      <c r="A73" s="9">
+        <v>93</v>
+      </c>
+      <c r="B73" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>370</v>
+      </c>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
@@ -4143,7 +4288,18 @@
       <c r="J73" s="6"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D74" s="6"/>
+      <c r="A74" s="9">
+        <v>94</v>
+      </c>
+      <c r="B74" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
@@ -4152,7 +4308,18 @@
       <c r="J74" s="6"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D75" s="6"/>
+      <c r="A75" s="9">
+        <v>95</v>
+      </c>
+      <c r="B75" s="10">
+        <v>46085</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D96ED3-A610-416F-BBB5-486378B37A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0900E9D5-52C4-4CD2-A895-F7AA2DAC3598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="384">
   <si>
     <t>Date</t>
   </si>
@@ -1491,6 +1491,54 @@
   </si>
   <si>
     <t xml:space="preserve">Gen ai model without using api using api </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro to genai </t>
+  </si>
+  <si>
+    <t>we build gen ai introduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gen ai practicle </t>
+  </si>
+  <si>
+    <t>we build gen ai model without using api key
+ai generate image with api key ( images are not accuracy miss to get project deal 
+we generatre few image 110 iter ita consume more memory 
+4time - you will get out of memory  on that scenario organization need to spend more pricing on memory which is not possible poc or r&amp;d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro to llm model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">llm tokenization -- BPE ( byte pair encoding ) -- it vocabular, 2 words, 3 words 
+word piece -- probability | sentence piece -- for langare chain &amp; japanes it create space holder to count as tokens 
+llm embedding -- rag &amp; vector datbase 
+transformer -- encoder, decoder &amp; encoder to decoder 
+attention -- one word multiple meansing to avoid context in llm to hallucinat model 
+simple self attend -- one word many measning | multi attention -- multiple word more meaning
+llm outdated -- pretrain required more traiing time number of hour each &amp; every llms 
+open ai api key generation | generatviu ai has 2 model -- text based model (LLM) language model cuz the trained form internet ( safe wesite -- wiki, research, xml, hugging face)
+when open ai spennd more money to train the heavy model -- they except some amount 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langchain poc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poc:1 -- langchain + open ai api key -- to generate text to text based model
+'Poc:2 - langchain + geminii api key -- to generat text based model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduce to langhcin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">langchain, langgrpah, langsmith
+opensoruce -- external tools, every framework has inbuild agent 
+langchain &amp; langgrah -- we can develop llm mode but langsmith we can monitor the model 
+explore about langchain documents , notes of from the official website 
+create opena i api key &amp; gemini api key 
+build text based model llm model with out trained nay data </t>
   </si>
 </sst>
 </file>
@@ -2018,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2779,6 +2827,55 @@
       </c>
       <c r="C68" s="2" t="s">
         <v>371</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A70" s="11">
+        <v>46085</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="216" x14ac:dyDescent="0.25">
+      <c r="A71" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+      <c r="A72" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="11">
+        <v>46088</v>
       </c>
     </row>
   </sheetData>
@@ -4327,8 +4424,19 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D76" s="6"/>
+    <row r="76" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="A76" s="9">
+        <v>96</v>
+      </c>
+      <c r="B76" s="10">
+        <v>46086</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>381</v>
+      </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0900E9D5-52C4-4CD2-A895-F7AA2DAC3598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B694B66A-A9C7-418F-A37E-D8A32C82E327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="401">
   <si>
     <t>Date</t>
   </si>
@@ -1539,6 +1539,64 @@
 explore about langchain documents , notes of from the official website 
 create opena i api key &amp; gemini api key 
 build text based model llm model with out trained nay data </t>
+  </si>
+  <si>
+    <t>llm ops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">langchsmith -- we are using for montiort result which given by langchain 
+we build custom bot using langhchina + open ai api key 
+langchain + gemini ai api key | we trace the model result &amp; Monitor all of them </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custome gpt using langchain, open ai api key , gemini ai api key </t>
+  </si>
+  <si>
+    <t>Text Based Model</t>
+  </si>
+  <si>
+    <t>Text - image using stable diffusion model</t>
+  </si>
+  <si>
+    <t>Multimodel - 1</t>
+  </si>
+  <si>
+    <t>Multimodel - 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable diffusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable diffusion model is gen ai technique which help to create multimodle 
+we learn how to create access token from Hugging face 
+from HF we downloaed all the models | use them 
+compvis - research grout to image gen model 2015
+2022 -- stabiliti ai change the name to stable diffusion model 
+social media, video game, fun activity , image gen model usin in the real time </t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable diffusion &amp; Huggin face </t>
+  </si>
+  <si>
+    <t>Multimodel - 3</t>
+  </si>
+  <si>
+    <t>Text to audio using stabilitio -- open ai whisper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text to Video -- we used wan ai | we got out of memory error  ( &gt;40gb pretrained) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugging Face </t>
+  </si>
+  <si>
+    <t>Text generation model (GPT2) &amp; NER ( Named entity Recognition)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project: sentiment anlaysis gradio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HF Poc </t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2873,9 +2931,34 @@
         <v>383</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="54" x14ac:dyDescent="0.25">
       <c r="A73" s="11">
         <v>46088</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="108" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -4445,7 +4528,18 @@
       <c r="J76" s="6"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D77" s="6"/>
+      <c r="A77" s="9">
+        <v>97</v>
+      </c>
+      <c r="B77" s="10">
+        <v>46087</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>386</v>
+      </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
@@ -4454,7 +4548,18 @@
       <c r="J77" s="6"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D78" s="6"/>
+      <c r="A78" s="9">
+        <v>98</v>
+      </c>
+      <c r="B78" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>388</v>
+      </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
@@ -4463,7 +4568,18 @@
       <c r="J78" s="6"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D79" s="6"/>
+      <c r="A79" s="9">
+        <v>99</v>
+      </c>
+      <c r="B79" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>395</v>
+      </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
@@ -4472,7 +4588,18 @@
       <c r="J79" s="6"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D80" s="6"/>
+      <c r="A80" s="9">
+        <v>100</v>
+      </c>
+      <c r="B80" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>396</v>
+      </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
@@ -4480,8 +4607,19 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D81" s="6"/>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="9">
+        <v>101</v>
+      </c>
+      <c r="B81" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>399</v>
+      </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
@@ -4489,8 +4627,19 @@
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
     </row>
-    <row r="82" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D82" s="6"/>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="9">
+        <v>102</v>
+      </c>
+      <c r="B82" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>398</v>
+      </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
@@ -4498,7 +4647,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4507,7 +4656,7 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
     </row>
-    <row r="84" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4516,7 +4665,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -4525,7 +4674,7 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
     </row>
-    <row r="86" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -4534,7 +4683,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -4543,7 +4692,7 @@
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
     </row>
-    <row r="88" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
@@ -4552,7 +4701,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
@@ -4561,7 +4710,7 @@
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
     </row>
-    <row r="90" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
@@ -4570,7 +4719,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
@@ -4579,7 +4728,7 @@
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
     </row>
-    <row r="92" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
@@ -4588,7 +4737,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
@@ -4597,7 +4746,7 @@
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
     </row>
-    <row r="94" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
@@ -4606,7 +4755,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
@@ -4615,7 +4764,7 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
     </row>
-    <row r="96" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B694B66A-A9C7-418F-A37E-D8A32C82E327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECC8BA8-81BD-4D95-BCD0-70E75A05516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="409">
   <si>
     <t>Date</t>
   </si>
@@ -1597,6 +1597,39 @@
   </si>
   <si>
     <t xml:space="preserve">HF Poc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">stable diffusion model we are completd 
+how to work with huggingface + stable diffusion model 
+why we need more infra or more configruation that’s we have done this 
+even kaggel also 30gb ( server will crash) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image - Image model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langgraph </t>
+  </si>
+  <si>
+    <t>we build chatbot usin single grph ( state - node &amp; edge -- end )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we build multinode graph </t>
+  </si>
+  <si>
+    <t>11-03-2026
+12-03-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langgraph built on top of langchain ecosystem 
+langgraph we built graph based agent  | langgraph workflow 
+user -- assgin task -- node will recive the task -- state -- node assign the task to edge state connect code tile -- edge will pass message to node -- ege -- end
+state -- node - edge - end 
+we builg singl graph we add just one node -- add messge | text based mode we built using langgraph 
+groq -- have you monitorned with langsmith | we dicussion recursion | factorial usin grecursion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rag </t>
   </si>
 </sst>
 </file>
@@ -2124,7 +2157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -2953,12 +2986,34 @@
         <v>392</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A75" s="11">
         <v>46091</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>393</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+      <c r="A76" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4648,7 +4703,18 @@
       <c r="J82" s="6"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D83" s="6"/>
+      <c r="A83" s="9">
+        <v>103</v>
+      </c>
+      <c r="B83" s="10">
+        <v>46092</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>402</v>
+      </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
@@ -4657,7 +4723,18 @@
       <c r="J83" s="6"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D84" s="6"/>
+      <c r="A84" s="9">
+        <v>104</v>
+      </c>
+      <c r="B84" s="10">
+        <v>46092</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>404</v>
+      </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
@@ -4666,7 +4743,18 @@
       <c r="J84" s="6"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D85" s="6"/>
+      <c r="A85" s="9">
+        <v>105</v>
+      </c>
+      <c r="B85" s="10">
+        <v>46093</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>405</v>
+      </c>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Mar 26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECC8BA8-81BD-4D95-BCD0-70E75A05516B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226A4E8D-FF88-4144-903C-C5D8A9A35476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="416">
   <si>
     <t>Date</t>
   </si>
@@ -1630,6 +1630,32 @@
   </si>
   <si>
     <t xml:space="preserve">Rag </t>
+  </si>
+  <si>
+    <t>Rag</t>
+  </si>
+  <si>
+    <t>Retraiver Augumented genearation using huggicefaceembedding, chroma db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we build rag | llm vs rag | llm fetch the data from internet 
+rag - fetch the data from db | RAG architecture | huggingface embedding is there 
+worked | most of the langchian model depricated | if you write the same code again after 1 month ( you will get bunch of error) | model deployeare getting issue still researchonly | </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemini AI </t>
+  </si>
+  <si>
+    <t>Llm model | Multimodel (Image - text )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gemini ai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">google deepmind research company of google 
+everytime they are come up new innovation ideas
+how mnay gemini provide | if you are create new api key then only 3 gemini model are accepted 
+3 pro | 3.1 flash | 3.1 flash lite preview </t>
   </si>
 </sst>
 </file>
@@ -2157,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3008,12 +3034,26 @@
         <v>407</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="72" x14ac:dyDescent="0.25">
       <c r="A77" s="11">
         <v>46094</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>408</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+      <c r="A78" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -4763,7 +4803,18 @@
       <c r="J85" s="6"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D86" s="6"/>
+      <c r="A86" s="9">
+        <v>106</v>
+      </c>
+      <c r="B86" s="10">
+        <v>46094</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>410</v>
+      </c>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
@@ -4772,7 +4823,18 @@
       <c r="J86" s="6"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D87" s="6"/>
+      <c r="A87" s="9">
+        <v>107</v>
+      </c>
+      <c r="B87" s="10">
+        <v>46097</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>413</v>
+      </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226A4E8D-FF88-4144-903C-C5D8A9A35476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AF17E5-1B6A-439A-9E10-353D6F27CD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="431">
   <si>
     <t>Date</t>
   </si>
@@ -1646,9 +1646,6 @@
     <t xml:space="preserve">Gemini AI </t>
   </si>
   <si>
-    <t>Llm model | Multimodel (Image - text )</t>
-  </si>
-  <si>
     <t xml:space="preserve">gemini ai </t>
   </si>
   <si>
@@ -1656,6 +1653,61 @@
 everytime they are come up new innovation ideas
 how mnay gemini provide | if you are create new api key then only 3 gemini model are accepted 
 3 pro | 3.1 flash | 3.1 flash lite preview </t>
+  </si>
+  <si>
+    <t xml:space="preserve">geminin ai &amp; cursor ide </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llm model | Multimodel (Image - text ) | UI </t>
+  </si>
+  <si>
+    <t>Cursor AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agenti AI ide to build application </t>
+  </si>
+  <si>
+    <t>gemini ai text based ui 
+gemini ai image base mode , 3.1 . 3proe, flash all model whcich has rag feature 
+cursor ai -- what could be reason organization are fireing employ 
+Introduce to nano banana</t>
+  </si>
+  <si>
+    <t>N8N AGENT</t>
+  </si>
+  <si>
+    <t>Chatbot using N8N workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N8n </t>
+  </si>
+  <si>
+    <t>N8n integration with Nano banana gemini 2.5 flash using openrouter</t>
+  </si>
+  <si>
+    <t>Nano Banana</t>
+  </si>
+  <si>
+    <t>Nano banana image editing , image createion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llama model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">llama model using huggingface &amp; groq </t>
+  </si>
+  <si>
+    <t>llama 3 &amp; llama 4
+3.1, 3.2, 3.3 , 4 maverick 4scout 
+can we donwload these directly -- hugging face, 11b vision model will unable to download 
+groq -- only llm | state of the art model it wont support 
+ollama but still you need to acces require more gpu mamory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepseek &amp; kimi k2 </t>
   </si>
 </sst>
 </file>
@@ -2183,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3050,10 +3102,40 @@
         <v>46097</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C78" s="2" t="s">
+    </row>
+    <row r="79" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+      <c r="A79" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>415</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A80" s="11">
+        <v>46099</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="11">
+        <v>46101</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -4833,7 +4915,7 @@
         <v>412</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
@@ -4843,7 +4925,18 @@
       <c r="J87" s="6"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D88" s="6"/>
+      <c r="A88" s="9">
+        <v>108</v>
+      </c>
+      <c r="B88" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>418</v>
+      </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
@@ -4852,7 +4945,18 @@
       <c r="J88" s="6"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D89" s="6"/>
+      <c r="A89" s="9">
+        <v>109</v>
+      </c>
+      <c r="B89" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>421</v>
+      </c>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
@@ -4861,7 +4965,18 @@
       <c r="J89" s="6"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D90" s="6"/>
+      <c r="A90" s="9">
+        <v>110</v>
+      </c>
+      <c r="B90" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>423</v>
+      </c>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
@@ -4870,7 +4985,18 @@
       <c r="J90" s="6"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D91" s="6"/>
+      <c r="A91" s="9">
+        <v>111</v>
+      </c>
+      <c r="B91" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>425</v>
+      </c>
       <c r="E91" s="6"/>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
@@ -4879,7 +5005,18 @@
       <c r="J91" s="6"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D92" s="6"/>
+      <c r="A92" s="9">
+        <v>112</v>
+      </c>
+      <c r="B92" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>428</v>
+      </c>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AF17E5-1B6A-439A-9E10-353D6F27CD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655D8FC7-D84B-457C-8FE3-83F977BFEB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="458">
   <si>
     <t>Date</t>
   </si>
@@ -1707,7 +1707,125 @@
 ollama but still you need to acces require more gpu mamory</t>
   </si>
   <si>
-    <t xml:space="preserve">deepseek &amp; kimi k2 </t>
+    <t xml:space="preserve">deepseek &amp; finetune llm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">finetunning -- metas llama model | finet tunn tehcnique -- lora &amp; qlora
+quantization -- quantized 64 bit to low bit 1b, 4b, 8bit || bitsanbytes
+accelearate | transformer   | these are reduce the weights model perform 
+meta llama model | lora_config (apply code paremter ) finetune
+deepssek code is very simplease ( ollam pull deepsekk) llm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prompt engineer </t>
+  </si>
+  <si>
+    <t>kimi k2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">openrouter.com | you get this model | work on it 
+kimi k2.5 we worked on openrouter also using ollama 
+all llm we understand | claude desktop  | n8n agent + gemini </t>
+  </si>
+  <si>
+    <t>Finetune Llms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lora &amp; Qlora using peft technique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepseek </t>
+  </si>
+  <si>
+    <t xml:space="preserve">llm using deepseek chainese model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">how to access llms using openrouter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we builg llm using kimi and streamlit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">openrouter </t>
+  </si>
+  <si>
+    <t>kimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we cannot build any llm model without prompt 
+when user enter any prompt few parameter effecte to the model llm model setting 
+1- model name ( model name ) 2. tempreature -- 0 to 2 | best temp value = 1
+low tempre --  no cohert response from internet | h igh temp -- most randomnes respone internet | temp - 1 
+top-p -- 0 to 1 | top - k range 0-1 | max value = 1 (probailiyt to create next token) 
+temp + top-p == would best combination | 1 &amp; 1 
+max lenght -- lenght of the tokens where user wants to generat ethe code 
+stop sequescen == terminator to end of the sentece. 
+frequnce penalty -- llm model never repets same words multiple times 
+out of dateleanring -- eveyr model are getting outdated to train updated data day on day
+rag | shot technique -- 0shot technqiue ( any promput llm responese proper) 1 shot technique -- give prompt using 1 exampel | few shot technque --= give prompt using more example 
+role playing prompt | self consitency prompt | cot technique (0cot, 1cot &amp; Few cot ) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prompt engineering practicle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">prompt engineer how to add parameters to change the results </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we generating promput using python input() print() loops list| 
+using function | generated prompuing  using format string | stepwise prompt 
+when we add api keys to this prompt model generat response 
+if we add llm model parameter model are behave based on parameter values 
+function vs lambda | super speed compare to the function 
+filter() map () reduce() filter even number | map to +2 or reduce all the output 
+from functools import reduce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">oops-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">class, method, object, constructor , self </t>
+  </si>
+  <si>
+    <t>python oops - 1</t>
+  </si>
+  <si>
+    <t>python oops - 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object , class 
+function vs method -- within class method &amp; without class function
+class 2 part -- Inbuild, user define, thread class, abstract class 
+method -- user define &amp; special | special method -- object statement will print automatically 
+__init__ is the constrctor ( self -- is points acts as argument also act as object ) 
+constructor &amp; self is very important in oops part 
+classname. methodname (self is not required ) | obj.methodname(self is must required) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encapsulation -- variables &amp; methods
+variable -- instance variable -- variable which declare inside __init__ 
+class variable -- variable which declare outside of __init __ 
+instance method --- user define the mehtod . That method which access all instance variance is called instance method | class method -- user define methd which access class variable (cls) argument and class method must declare with decorator @classmethod | static method -- method which has nothing do work with any class or instance that is calle static method &amp; also we need to define @  staticmethod 
+inhertience - inherit one class to another class is called inheritence  
+single level inheritence -- single level inheritence alwasy work with minimum 2 class 
+multilevel inheritence -- multilevel inheritence alwasy works with more then 2 class 
+multiple inheritence -- if one class call with other class  
+contstructor in inheritence | super() in inheritence | method resoltuion order in inhertence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGENTIC AI </t>
+  </si>
+  <si>
+    <t>oops-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encapsulation, Inhertience </t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenti ai ide </t>
+  </si>
+  <si>
+    <t xml:space="preserve">antigravity , cline is working for everybody </t>
   </si>
 </sst>
 </file>
@@ -2235,7 +2353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3130,12 +3248,78 @@
         <v>429</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A81" s="11">
         <v>46101</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>430</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="54" x14ac:dyDescent="0.25">
+      <c r="A82" s="11">
+        <v>46104</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="234" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>46106</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+      <c r="A84" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="126" x14ac:dyDescent="0.25">
+      <c r="A85" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="216" x14ac:dyDescent="0.25">
+      <c r="A86" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -3152,7 +3336,7 @@
     <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="82.109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="78.21875" style="7" customWidth="1"/>
     <col min="5" max="5" width="73.88671875" style="7" customWidth="1"/>
     <col min="6" max="6" width="23.21875" style="7" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="7" customWidth="1"/>
@@ -4070,7 +4254,7 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:10" ht="140.4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="156" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
         <v>281</v>
       </c>
@@ -4764,7 +4948,7 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>100</v>
       </c>
@@ -5025,7 +5209,18 @@
       <c r="J92" s="6"/>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D93" s="6"/>
+      <c r="A93" s="9">
+        <v>113</v>
+      </c>
+      <c r="B93" s="10">
+        <v>46100</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>436</v>
+      </c>
       <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
@@ -5034,7 +5229,18 @@
       <c r="J93" s="6"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D94" s="6"/>
+      <c r="A94" s="9">
+        <v>114</v>
+      </c>
+      <c r="B94" s="10">
+        <v>46101</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>438</v>
+      </c>
       <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
@@ -5043,7 +5249,18 @@
       <c r="J94" s="6"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D95" s="6"/>
+      <c r="A95" s="9">
+        <v>115</v>
+      </c>
+      <c r="B95" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>439</v>
+      </c>
       <c r="E95" s="6"/>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
@@ -5052,7 +5269,18 @@
       <c r="J95" s="6"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D96" s="6"/>
+      <c r="A96" s="9">
+        <v>116</v>
+      </c>
+      <c r="B96" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>440</v>
+      </c>
       <c r="E96" s="6"/>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
@@ -5060,8 +5288,19 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D97" s="6"/>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="9">
+        <v>117</v>
+      </c>
+      <c r="B97" s="10">
+        <v>46107</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>445</v>
+      </c>
       <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
@@ -5069,8 +5308,19 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
     </row>
-    <row r="98" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D98" s="6"/>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="9">
+        <v>118</v>
+      </c>
+      <c r="B98" s="10">
+        <v>46108</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>448</v>
+      </c>
       <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
@@ -5078,8 +5328,19 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D99" s="6"/>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="9">
+        <v>119</v>
+      </c>
+      <c r="B99" s="10">
+        <v>46111</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>455</v>
+      </c>
       <c r="E99" s="6"/>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
@@ -5087,8 +5348,19 @@
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
     </row>
-    <row r="100" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D100" s="6"/>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="9">
+        <v>120</v>
+      </c>
+      <c r="B100" s="10">
+        <v>46113</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>457</v>
+      </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
@@ -5096,7 +5368,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
@@ -5105,7 +5377,7 @@
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
     </row>
-    <row r="102" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -5114,7 +5386,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
@@ -5123,7 +5395,7 @@
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
     </row>
-    <row r="104" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -5132,7 +5404,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -5141,7 +5413,7 @@
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
     </row>
-    <row r="106" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -5150,7 +5422,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -5159,7 +5431,7 @@
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
     </row>
-    <row r="108" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
@@ -5168,7 +5440,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
@@ -5177,7 +5449,7 @@
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
     </row>
-    <row r="110" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
@@ -5186,7 +5458,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -5195,7 +5467,7 @@
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
     </row>
-    <row r="112" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655D8FC7-D84B-457C-8FE3-83F977BFEB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDDA375-53A5-4238-A003-2041992B1CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="466">
   <si>
     <t>Date</t>
   </si>
@@ -1826,6 +1826,39 @@
   </si>
   <si>
     <t xml:space="preserve">antigravity , cline is working for everybody </t>
+  </si>
+  <si>
+    <t xml:space="preserve">blackbox agent, kilo code, codex --  openai </t>
+  </si>
+  <si>
+    <t>python</t>
+  </si>
+  <si>
+    <t>OOPS we completed</t>
+  </si>
+  <si>
+    <t>agentic ai ide -- blackbox, codex, kilo code, bunch of agents are available 
+polymohism -- one feature many from 
+duck typing -- different class but methods should same 
+operator overlaoding -- __add__, __sub__ ( using help of these methods we are using operator)
+method overloading ( method overload using default argumnet, variable length
+method overriding - paranet class method overrid to child class method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abstraction, multithreading </t>
+  </si>
+  <si>
+    <t>abstract class &amp; abstract method
+from abc import ABC, abstract method  | abstract method has only declaration but no defination 
+the class which carries abstract method is called abstract class 
+multithreading | multiple thread runs mutliple processor at same time 
+code runs using multithread process</t>
+  </si>
+  <si>
+    <t>Agentic AI(smolagents)</t>
+  </si>
+  <si>
+    <t>single agent using smol agent with code agent with ddgs &amp; websearch tool</t>
   </si>
 </sst>
 </file>
@@ -1886,12 +1919,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1899,6 +1934,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1906,6 +1942,7 @@
       <sz val="11"/>
       <color theme="5"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2353,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3314,12 +3351,31 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="108" x14ac:dyDescent="0.25">
       <c r="A87" s="11">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>453</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A88" s="11">
+        <v>46114</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="11">
+        <v>46115</v>
       </c>
     </row>
   </sheetData>
@@ -5369,7 +5425,18 @@
       <c r="J100" s="6"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D101" s="6"/>
+      <c r="A101" s="9">
+        <v>121</v>
+      </c>
+      <c r="B101" s="10">
+        <v>46114</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>458</v>
+      </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
@@ -5378,7 +5445,18 @@
       <c r="J101" s="6"/>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D102" s="6"/>
+      <c r="A102" s="9">
+        <v>122</v>
+      </c>
+      <c r="B102" s="10">
+        <v>46114</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
@@ -5387,7 +5465,18 @@
       <c r="J102" s="6"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D103" s="6"/>
+      <c r="A103" s="9">
+        <v>123</v>
+      </c>
+      <c r="B103" s="10">
+        <v>46115</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>465</v>
+      </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDDA375-53A5-4238-A003-2041992B1CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD7E909-B7D5-4ABF-8A4A-E2CDE0B069FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="472">
   <si>
     <t>Date</t>
   </si>
@@ -1859,6 +1859,34 @@
   </si>
   <si>
     <t>single agent using smol agent with code agent with ddgs &amp; websearch tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentic ai workflows | agentic ai components
+		agents -- autonomus system that can perceive, think, complete the goal 
+		environment - the context where agents will operate ( website, api call, database) 
+		perception -- how the agents gather informatio (api, sensor, tools etc) 
+		memory -- short term memory &amp; long term memory 
+		planning -- the agent is able to break complex task to easy and complete the job 
+		decission engine -- rules , logics | | tool use -- websearch , api, database, cloud integration 
+		learning -- agent learn from mistake (feedback loop) 
+		goal allignment -- master is right prompt and complete the goal  
+code agent is connected tool called ddgs _ agetne fetch information for us | function to build svm model </t>
+  </si>
+  <si>
+    <t>AGENTIC AI (smolagents)</t>
+  </si>
+  <si>
+    <t>Agentic AI(Langchain Agents)</t>
+  </si>
+  <si>
+    <t>langchain agents are interactiing with pandas_dataframe_agent</t>
+  </si>
+  <si>
+    <t>AGENTIC AI (Langchain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agents are interact with pandas_agent
+langchin agents are interact with multidataframe | ask prompt and agent build the task for us </t>
   </si>
 </sst>
 </file>
@@ -2390,7 +2418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3373,9 +3401,26 @@
         <v>463</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="180" x14ac:dyDescent="0.25">
       <c r="A89" s="11">
         <v>46115</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="A90" s="11">
+        <v>46116</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -5485,7 +5530,18 @@
       <c r="J103" s="6"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D104" s="6"/>
+      <c r="A104" s="9">
+        <v>124</v>
+      </c>
+      <c r="B104" s="10">
+        <v>46116</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
       <c r="G104" s="6"/>

--- a/Regular Summarization_ 530 PM.xlsx
+++ b/Regular Summarization_ 530 PM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIT\1. NIT_Batches\2. EVENING BATCH\N_Batch -- 5.30PM -- Apr 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD7E909-B7D5-4ABF-8A4A-E2CDE0B069FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312A7367-96DB-46A6-9585-AA43F1C99DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18th July - Agenda Sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="500">
   <si>
     <t>Date</t>
   </si>
@@ -1887,6 +1887,103 @@
   <si>
     <t xml:space="preserve">agents are interact with pandas_agent
 langchin agents are interact with multidataframe | ask prompt and agent build the task for us </t>
+  </si>
+  <si>
+    <t>AGENTIC AI (phidata)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phidata also called as agno agi 
+we checked the phi data documenttion part 
+we understand like how agent + interact with llm + tools 
+tools -- yfinance | ddgs | websearch | list of tool to intergrate for difference scenario 
+news agent | cricket agent | ollama | python function -- build multiple way </t>
+  </si>
+  <si>
+    <t>125 - 129</t>
+  </si>
+  <si>
+    <t>Agentic AI(Phi data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- phi data single agent with yfinance &amp; multi agent -- create team of agent
+2- multiagent using news agent 
+3- cricket agent multi agent ( opneai &amp; google gemini)
+4- agent building using python function 
+5- multiagent using ollama + phi data &amp; langchain ollama </t>
+  </si>
+  <si>
+    <t>Agentic AI(Crew data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiagent using open ai  &amp; GOOGLE GEMINI serper api key </t>
+  </si>
+  <si>
+    <t>AGENTIC AI (Crew AI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model context protocol connected to claude </t>
+  </si>
+  <si>
+    <t>MCP</t>
+  </si>
+  <si>
+    <t>09-04-2026
+10-04-2026</t>
+  </si>
+  <si>
+    <t>mcp using claude desktop 
+mcp using -- cline, antigravity, cursor, blackbox agentic ide</t>
+  </si>
+  <si>
+    <t>MCP-2</t>
+  </si>
+  <si>
+    <t>MCP-1</t>
+  </si>
+  <si>
+    <t>mcp using -- cline, antigravity, cursor, blackbox agentic ide</t>
+  </si>
+  <si>
+    <t>Fast API</t>
+  </si>
+  <si>
+    <t>openclaw</t>
+  </si>
+  <si>
+    <t>openclaw + gemini + telegram agent</t>
+  </si>
+  <si>
+    <t>openclaw agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claude </t>
+  </si>
+  <si>
+    <t>fastapi , cowork , claude code in ollama, claude llms ( sonnete, haiku, opus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">codex + mlops </t>
+  </si>
+  <si>
+    <t xml:space="preserve">codex another desktop agent works same like cowork it slower compare to claude
+mlops -- fusion between datascientist, data engineer, devops 
+after machine + monitored by operation team | mlflow track log, metrics, perform 
+compare models using mlfow traces, artifact created by mlflow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlops + cicd pipeline </t>
+  </si>
+  <si>
+    <t>codex</t>
+  </si>
+  <si>
+    <t>codex desktop -- multiagent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlops </t>
+  </si>
+  <si>
+    <t>build mlops using mlfow ui &amp; model registrr</t>
   </si>
 </sst>
 </file>
@@ -2046,7 +2143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2121,6 +2218,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2418,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="3" customWidth="1"/>
@@ -3423,6 +3523,91 @@
         <v>471</v>
       </c>
     </row>
+    <row r="91" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A91" s="11">
+        <v>46118</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="78" x14ac:dyDescent="0.25">
+      <c r="A92" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="36" x14ac:dyDescent="0.25">
+      <c r="A94" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="25">
+        <v>46123</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="72" x14ac:dyDescent="0.25">
+      <c r="A97" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3434,7 +3619,7 @@
   <dimension ref="A1:K280"/>
   <sheetFormatPr defaultColWidth="13.77734375" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" style="7" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" style="7" customWidth="1"/>
     <col min="3" max="3" width="33.44140625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="78.21875" style="7" customWidth="1"/>
@@ -5549,8 +5734,19 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D105" s="6"/>
+    <row r="105" spans="1:10" ht="78" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B105" s="10">
+        <v>46118</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>476</v>
+      </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
       <c r="G105" s="6"/>
@@ -5559,7 +5755,18 @@
       <c r="J105" s="6"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D106" s="6"/>
+      <c r="A106" s="9">
+        <v>130</v>
+      </c>
+      <c r="B106" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
       <c r="G106" s="6"/>
@@ -5568,7 +5775,18 @@
       <c r="J106" s="6"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D107" s="6"/>
+      <c r="A107" s="9">
+        <v>131</v>
+      </c>
+      <c r="B107" s="10">
+        <v>46120</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>480</v>
+      </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
@@ -5577,7 +5795,18 @@
       <c r="J107" s="6"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D108" s="6"/>
+      <c r="A108" s="9">
+        <v>132</v>
+      </c>
+      <c r="B108" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>486</v>
+      </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
@@ -5585,8 +5814,19 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D109" s="6"/>
+    <row r="109" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A109" s="9">
+        <v>133</v>
+      </c>
+      <c r="B109" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>489</v>
+      </c>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
       <c r="G109" s="6"/>
@@ -5595,7 +5835,18 @@
       <c r="J109" s="6"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D110" s="6"/>
+      <c r="A110" s="9">
+        <v>134</v>
+      </c>
+      <c r="B110" s="10">
+        <v>46125</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>492</v>
+      </c>
       <c r="E110" s="6"/>
       <c r="F110" s="6"/>
       <c r="G110" s="6"/>
@@ -5604,7 +5855,18 @@
       <c r="J110" s="6"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D111" s="6"/>
+      <c r="A111" s="9">
+        <v>135</v>
+      </c>
+      <c r="B111" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>497</v>
+      </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
       <c r="G111" s="6"/>
@@ -5613,7 +5875,18 @@
       <c r="J111" s="6"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D112" s="6"/>
+      <c r="A112" s="9">
+        <v>136</v>
+      </c>
+      <c r="B112" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>499</v>
+      </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
       <c r="G112" s="6"/>
@@ -5621,7 +5894,10 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="9">
+        <v>137</v>
+      </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -5630,7 +5906,7 @@
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
     </row>
-    <row r="114" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
@@ -5639,7 +5915,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -5648,7 +5924,7 @@
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
     </row>
-    <row r="116" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -5657,7 +5933,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
       <c r="F117" s="6"/>
@@ -5666,7 +5942,7 @@
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
     </row>
-    <row r="118" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
       <c r="F118" s="6"/>
@@ -5675,7 +5951,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
       <c r="F119" s="6"/>
@@ -5684,7 +5960,7 @@
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
     </row>
-    <row r="120" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
       <c r="F120" s="6"/>
@@ -5693,7 +5969,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
       <c r="F121" s="6"/>
@@ -5702,7 +5978,7 @@
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
     </row>
-    <row r="122" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
       <c r="F122" s="6"/>
@@ -5711,7 +5987,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -5720,7 +5996,7 @@
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
     </row>
-    <row r="124" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -5729,7 +6005,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -5738,7 +6014,7 @@
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
     </row>
-    <row r="126" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -5747,7 +6023,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -5756,7 +6032,7 @@
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
     </row>
-    <row r="128" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
